--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -31,14 +31,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="0.0000%"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -123,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,14 +138,13 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -793,35 +791,38 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>PP&amp;E, ROU, intangibles &amp; inv. property</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>92000</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>95500</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>126436</v>
-      </c>
-      <c r="E6" s="20">
+          <t>Net fixed &amp; intangible assets (PP&amp;E, ROU, intangibles, inv. prop.)</t>
+        </is>
+      </c>
+      <c r="B6" s="17">
+        <f>B12-B7-B8-B9-B10-B11</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
+        <f>C12-C7-C8-C9-C10-C11</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>D12-D7-D8-D9-D10-D11</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
         <f>D6+Segments!E20*Assumptions!$C$60+'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <f>E6+Segments!F20*Assumptions!$D$60+'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <f>F6+Segments!G20*Assumptions!$E$60+'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <f>G6+Segments!H20*Assumptions!$F$60+'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="19">
         <f>H6+Segments!I20*Assumptions!$G$60+'Income Statement'!I11</f>
         <v/>
       </c>
@@ -841,23 +842,23 @@
       <c r="D7" s="9" t="n">
         <v>4641</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <f>D7</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>E7</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>F7</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <f>G7</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <f>H7</f>
         <v/>
       </c>
@@ -877,23 +878,23 @@
       <c r="D8" s="9" t="n">
         <v>24893</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>D8</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>E8</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f>F8</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <f>G8</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <f>H8</f>
         <v/>
       </c>
@@ -913,23 +914,23 @@
       <c r="D9" s="9" t="n">
         <v>26727</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <f>D9+Segments!E20*Assumptions!$C$61</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <f>E9+Segments!F20*Assumptions!$D$61</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <f>F9+Segments!G20*Assumptions!$E$61</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="19">
         <f>G9+Segments!H20*Assumptions!$F$61</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="19">
         <f>H9+Segments!I20*Assumptions!$G$61</f>
         <v/>
       </c>
@@ -947,26 +948,26 @@
         <v>30755</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>15108</v>
-      </c>
-      <c r="E10" s="20">
-        <f>'Cash Flow'!E20</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>'Cash Flow'!F20</f>
-        <v/>
-      </c>
-      <c r="G10" s="20">
-        <f>'Cash Flow'!G20</f>
-        <v/>
-      </c>
-      <c r="H10" s="20">
-        <f>'Cash Flow'!H20</f>
-        <v/>
-      </c>
-      <c r="I10" s="20">
-        <f>'Cash Flow'!I20</f>
+        <v>15080</v>
+      </c>
+      <c r="E10" s="19">
+        <f>'Cash Flow'!E16</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>'Cash Flow'!F16</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>'Cash Flow'!G16</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>'Cash Flow'!H16</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>'Cash Flow'!I16</f>
         <v/>
       </c>
     </row>
@@ -976,71 +977,68 @@
           <t>Other assets</t>
         </is>
       </c>
-      <c r="B11" s="18">
-        <f>159646-B6-B7-B8-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C11" s="18">
-        <f>160638-C6-C7-C8-C9-C10</f>
-        <v/>
+      <c r="B11" s="9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>2600</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>2952</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>D11</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>E11</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>F11</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <f>G11</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <f>H11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="24" t="n">
         <v>159646</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="24" t="n">
         <v>160638</v>
       </c>
-      <c r="D12" s="28">
-        <f>SUM(D6:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="21">
+      <c r="D12" s="24" t="n">
+        <v>157477</v>
+      </c>
+      <c r="E12" s="27">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="27">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="27">
         <f>SUM(G6:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="27">
         <f>SUM(H6:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="27">
         <f>SUM(I6:I11)</f>
         <v/>
       </c>
@@ -1060,23 +1058,23 @@
       <c r="D14" s="9" t="n">
         <v>83414</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <f>D14+'Income Statement'!E19-Assumptions!$C$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <f>E14+'Income Statement'!F19-Assumptions!$D$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="19">
         <f>F14+'Income Statement'!G19-Assumptions!$E$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="19">
         <f>G14+'Income Statement'!H19-Assumptions!$F$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="19">
         <f>H14+'Income Statement'!I19-Assumptions!$G$66*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -1096,62 +1094,62 @@
       <c r="D15" s="9" t="n">
         <v>3482</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <f>D15-'Income Statement'!E18</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <f>E15-'Income Statement'!F18</f>
         <v/>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="19">
         <f>F15-'Income Statement'!G18</f>
         <v/>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="19">
         <f>G15-'Income Statement'!H18</f>
         <v/>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="19">
         <f>H15-'Income Statement'!I18</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <f>B14+B15</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f>G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <f>H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <f>I14+I15</f>
         <v/>
       </c>
@@ -1171,23 +1169,23 @@
       <c r="D17" s="9" t="n">
         <v>15191</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <f>D17+7284</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <f>E17</f>
         <v/>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <f>F17</f>
         <v/>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="17">
         <f>G17</f>
         <v/>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="17">
         <f>H17</f>
         <v/>
       </c>
@@ -1207,23 +1205,23 @@
       <c r="D18" s="9" t="n">
         <v>2253</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <f>D18</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <f>E18</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <f>F18</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <f>G18</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <f>H18</f>
         <v/>
       </c>
@@ -1235,31 +1233,31 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>27500</v>
+        <v>26500</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>29610</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <f>D19</f>
         <v/>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <f>E19</f>
         <v/>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <f>F19</f>
         <v/>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="17">
         <f>G19</f>
         <v/>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="17">
         <f>H19</f>
         <v/>
       </c>
@@ -1270,112 +1268,113 @@
           <t>Zakat payable, provisions &amp; other liabilities</t>
         </is>
       </c>
-      <c r="B20" s="18">
-        <f>159646-B16-B17-B18-B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f>160638-C16-C17-C18-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>14876</v>
-      </c>
-      <c r="E20" s="18">
+      <c r="B20" s="17">
+        <f>B12-B16-B17-B18-B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>C12-C16-C17-C18-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>D12-D16-D17-D18-D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
         <f>D20</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <f>E20</f>
         <v/>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="17">
         <f>F20</f>
         <v/>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="17">
         <f>G20</f>
         <v/>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <f>H20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>TOTAL EQUITY &amp; LIABILITIES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>B16+B17+B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>C16+C17+C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>D16+D17+D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <f>E16+E17+E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="20">
         <f>F16+F17+F18+F19+F20</f>
         <v/>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="20">
         <f>G16+G17+G18+G19+G20</f>
         <v/>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="20">
         <f>H16+H17+H18+H19+H20</f>
         <v/>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="20">
         <f>I16+I17+I18+I19+I20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Balance check (assets − L&amp;E)</t>
         </is>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="28">
         <f>B12-B21</f>
         <v/>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="28">
         <f>C12-C21</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <f>D12-D21</f>
         <v/>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="20">
         <f>E12-E21</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="20">
         <f>F12-F21</f>
         <v/>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="20">
         <f>G12-G21</f>
         <v/>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="20">
         <f>H12-H21</f>
         <v/>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="20">
         <f>I12-I21</f>
         <v/>
       </c>
@@ -1386,37 +1385,44 @@
           <t>Net debt — IR basis (borrowings − cash, group def.)</t>
         </is>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="28">
         <f>B17-B10</f>
         <v/>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="28">
         <f>C17-C10</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="28">
         <f>D17-D10</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <f>E17-E10</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="17">
         <f>F17-F10</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="17">
         <f>G17-G10</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="17">
         <f>H17-H10</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="17">
         <f>I17-I10</f>
         <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Historic mapping: disclosed IR anchors (total assets, cash+murabaha, total debt, attributable equity) are blue as reported; FY25 line detail (associates 4,641 · financial assets 24,893 · receivables 26,727 · leases 2,253 · payables+financial liabilities 29,610 · NCI 3,482) is from the Q1-2026 FS 31-Dec-25 comparatives; FY23/FY24 line detail is estimated to tie to the disclosed totals (flagged). "Net fixed &amp; intangible assets" and "Zakat payable, provisions &amp; other liabilities" are the balancing lines — shown as formulas off the disclosed totals, so the balance check is exact in every column. FY26E borrowings step up SAR +7,284mn (the completed Jan-2026 $2bn sukuk net of amortisation); gross debt flat thereafter. Two cash framings: FS cash incl. stc bank (21,442 at Q1-26) vs IR core-group cash (15,412) — the model rolls the IR-basis series (FY25: 15,080).</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1509,23 +1515,23 @@
           <t>Profit for the period (incl. NCI)</t>
         </is>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f>'Income Statement'!E16</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <f>'Income Statement'!F16</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <f>'Income Statement'!G16</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <f>'Income Statement'!H16</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="19">
         <f>'Income Statement'!I16</f>
         <v/>
       </c>
@@ -1536,23 +1542,23 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <f>-'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <f>-'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <f>-'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <f>-'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="19">
         <f>-'Income Statement'!I11</f>
         <v/>
       </c>
@@ -1563,50 +1569,50 @@
           <t>− Increase in trade receivables (ΔWC)</t>
         </is>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <f>-(('Balance Sheet'!E9)-('Balance Sheet'!D9))</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <f>-(('Balance Sheet'!F9)-('Balance Sheet'!E9))</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="19">
         <f>-(('Balance Sheet'!G9)-('Balance Sheet'!F9))</f>
         <v/>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <f>-(('Balance Sheet'!H9)-('Balance Sheet'!G9))</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="19">
         <f>-(('Balance Sheet'!I9)-('Balance Sheet'!H9))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <f>SUM(E6:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <f>SUM(F6:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <f>SUM(I6:I8)</f>
         <v/>
       </c>
@@ -1617,50 +1623,50 @@
           <t>− Capex</t>
         </is>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <f>-Segments!E20*Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <f>-Segments!F20*Assumptions!$D$60</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <f>-Segments!G20*Assumptions!$E$60</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <f>-Segments!H20*Assumptions!$F$60</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="19">
         <f>-Segments!I20*Assumptions!$G$60</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <f>E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <f>F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="20">
         <f>G9+G10</f>
         <v/>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="20">
         <f>H9+H10</f>
         <v/>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="20">
         <f>I9+I10</f>
         <v/>
       </c>
@@ -1671,23 +1677,23 @@
           <t>+ Increase in borrowings (net)</t>
         </is>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>7284</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="17">
         <f>0</f>
         <v/>
       </c>
@@ -1698,50 +1704,50 @@
           <t>− Dividends paid (attributable)</t>
         </is>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <f>-Assumptions!$C$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="19">
         <f>-Assumptions!$D$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="19">
         <f>-Assumptions!$E$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="19">
         <f>-Assumptions!$F$66*Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="19">
         <f>-Assumptions!$G$66*Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f>E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f>F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f>G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <f>H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <f>I11+I12+I13</f>
         <v/>
       </c>
@@ -1752,50 +1758,50 @@
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="19">
         <f>'Balance Sheet'!D10</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>E16</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <f>F16</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <f>G16</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="17">
         <f>H16</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E15+E14</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f>F15+F14</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f>G15+G14</f>
         <v/>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <f>H15+H14</f>
         <v/>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <f>I15+I14</f>
         <v/>
       </c>
@@ -1900,301 +1906,301 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <f>'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <f>'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <f>'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f>'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <f>'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <f>'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <f>'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="19">
         <f>'Income Statement'!I6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f>'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <f>'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <f>'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="19">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <f>'Income Statement'!B12</f>
         <v/>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <f>'Income Statement'!C12</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <f>'Income Statement'!D12</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <f>'Income Statement'!F12</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="19">
         <f>'Income Statement'!G12</f>
         <v/>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <f>'Income Statement'!H12</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="19">
         <f>'Income Statement'!I12</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Net profit (attributable)</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <f>'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <f>'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <f>'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <f>'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="19">
         <f>'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="19">
         <f>'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="19">
         <f>'Income Statement'!I19</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <f>'Balance Sheet'!B12</f>
         <v/>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <f>'Balance Sheet'!C12</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <f>'Balance Sheet'!D12</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <f>'Balance Sheet'!E12</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <f>'Balance Sheet'!F12</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <f>'Balance Sheet'!G12</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <f>'Balance Sheet'!H12</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="19">
         <f>'Balance Sheet'!I12</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="19">
         <f>'Balance Sheet'!B16</f>
         <v/>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <f>'Balance Sheet'!C16</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <f>'Balance Sheet'!D16</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <f>'Balance Sheet'!E16</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="19">
         <f>'Balance Sheet'!F16</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="19">
         <f>'Balance Sheet'!G16</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="19">
         <f>'Balance Sheet'!H16</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="19">
         <f>'Balance Sheet'!I16</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Net debt (IR basis)</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="19">
         <f>'Balance Sheet'!B24</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="19">
         <f>'Balance Sheet'!C24</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="19">
         <f>'Balance Sheet'!D24</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <f>'Balance Sheet'!E24</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="19">
         <f>'Balance Sheet'!F24</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="19">
         <f>'Balance Sheet'!G24</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="19">
         <f>'Balance Sheet'!H24</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="19">
         <f>'Balance Sheet'!I24</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Free cash flow (forecast)</t>
         </is>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="19">
         <f>'Cash Flow'!E11</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="19">
         <f>'Cash Flow'!F11</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="19">
         <f>'Cash Flow'!G11</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="19">
         <f>'Cash Flow'!H11</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="19">
         <f>'Cash Flow'!I11</f>
         <v/>
       </c>
@@ -2226,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2261,67 +2267,67 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>The probability read (T+60)</t>
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>The probability read (3 months)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>P(price above spot)</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>0.54426</v>
+      <c r="B6" s="18" t="n">
+        <v>0.56274</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>P(+10%) vs P(−10%) — odds</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>11% vs 7% · 1.7:1</t>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>16% vs 8% · 2.0:1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Median level (SAR) and % move</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>45.06 (+0.8%)</t>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>45.30 (+1.3%)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>50% band (25th–75th)</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>43.0 – 47.2  (-3.8% / +5.5%)</t>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>42.9 – 47.9  (-4.2% / +7.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Touch(+10%) / touch(−10%)</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
-        <is>
-          <t>19% / 12%</t>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>27% / 16%</t>
         </is>
       </c>
     </row>
@@ -2365,47 +2371,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>T+20 sessions</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n">
         <v>41.7</v>
       </c>
-      <c r="C14" s="27" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D14" s="27" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="F14" s="27" t="n">
-        <v>48.2</v>
+      <c r="C14" s="26" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>48.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>T+60 sessions</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="C15" s="27" t="n">
-        <v>43</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>51.2</v>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>52.2</v>
       </c>
     </row>
     <row r="17">
@@ -2416,148 +2422,137 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Anchor volatility (HAR, annualized)</t>
-        </is>
-      </c>
-      <c r="B18" s="32">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Forward volatility over three months (annualised)</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
         <f>Assumptions!$B$37</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Secular drift (daily) — zero-drift class</t>
-        </is>
-      </c>
-      <c r="B19" s="32">
-        <f>Assumptions!$B$38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Net factor drift / quarter</t>
-        </is>
-      </c>
-      <c r="B20" s="32">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Momentum lean applied over three months</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
         <f>Assumptions!$B$39</f>
         <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Level-touch ladder (probability of touching by horizon)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Level-touch ladder (probability of touching by horizon)</t>
+          <t>Level (SAR)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>3 months</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Level (SAR)</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>T+20</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>T+60</t>
-        </is>
+      <c r="A23" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>0.20038</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>0.02346</v>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>0.13418</v>
+      <c r="A24" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>0.11476</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>0.40734</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n">
-        <v>48</v>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>0.09494</v>
-      </c>
-      <c r="C25" s="19" t="n">
-        <v>0.3138</v>
+      <c r="A25" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>0.48074</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>0.72196</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
-        <v>46</v>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>0.42702</v>
-      </c>
-      <c r="C26" s="19" t="n">
-        <v>0.65984</v>
+      <c r="A26" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>0.59512</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>0.7541600000000001</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n">
-        <v>44</v>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>0.5667</v>
-      </c>
-      <c r="C27" s="19" t="n">
-        <v>0.72556</v>
+      <c r="A27" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>0.11542</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>0.35908</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
-        <v>42</v>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>0.11068</v>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>0.30474</v>
+      <c r="A28" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>0.01328</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>0.13696</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="B29" s="19" t="n">
-        <v>0.02038</v>
-      </c>
-      <c r="C29" s="19" t="n">
-        <v>0.10814</v>
+      <c r="A29" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>0.04186</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
-        <v>38</v>
-      </c>
-      <c r="B30" s="19" t="n">
-        <v>0.00476</v>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>0.03742</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="n">
+      <c r="A30" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="B31" s="19" t="n">
-        <v>0.00112</v>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>0.01378</v>
+      <c r="B30" s="18" t="n">
+        <v>0.00018</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>0.01182</v>
       </c>
     </row>
   </sheetData>
@@ -2611,143 +2606,143 @@
           <t>WACC \ terminal g</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>0.015</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="36" t="n">
         <v>0.02</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="36" t="n">
         <v>0.025</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="36" t="n">
         <v>0.03</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="36" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="18" t="n">
         <v>0.07132614912126105</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A6-B$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A6-C$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A6-D$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A6-E$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A6-F$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="18" t="n">
         <v>0.07632614912126104</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A7-B$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A7-C$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A7-D$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A7-E$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A7-F$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="37" t="n">
         <v>0.08132614912126104</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A8-B$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A8-C$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A8-D$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A8-E$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A8-F$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="18" t="n">
         <v>0.08632614912126105</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A9-B$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A9-C$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A9-D$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A9-E$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A9-F$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="18" t="n">
         <v>0.09132614912126104</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A10-B$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A10-C$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A10-D$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A10-E$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A10-F$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2767,22 +2762,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Ke (rating ERP)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>DCF value/sh</t>
         </is>
@@ -2792,15 +2787,15 @@
       <c r="A16" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>Assumptions!$B$10+A16*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <f>(1-Assumptions!$B$16)*B16+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C16)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C16-Assumptions!$B$18)/(1+C16)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2809,15 +2804,15 @@
       <c r="A17" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <f>Assumptions!$B$10+A17*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="18">
         <f>(1-Assumptions!$B$16)*B17+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C17)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C17-Assumptions!$B$18)/(1+C17)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2831,15 +2826,15 @@
       <c r="A18" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <f>Assumptions!$B$10+A18*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="18">
         <f>(1-Assumptions!$B$16)*B18+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C18)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C18-Assumptions!$B$18)/(1+C18)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2848,15 +2843,15 @@
       <c r="A19" s="7" t="n">
         <v>0.85</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <f>Assumptions!$B$10+A19*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="18">
         <f>(1-Assumptions!$B$16)*B19+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C19)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C19-Assumptions!$B$18)/(1+C19)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2865,15 +2860,15 @@
       <c r="A20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>Assumptions!$B$10+A20*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="18">
         <f>(1-Assumptions!$B$16)*B20+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C20)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C20-Assumptions!$B$18)/(1+C20)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2887,15 +2882,15 @@
       <c r="A21" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <f>Assumptions!$B$10+A21*Assumptions!$B$12</f>
         <v/>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="18">
         <f>(1-Assumptions!$B$16)*B21+Assumptions!$B$16*Assumptions!$B$15</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C21)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C21-Assumptions!$B$18)/(1+C21)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -2993,46 +2988,46 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>'Income Statement'!B19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <f>'Income Statement'!C19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <f>'Income Statement'!D19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="26">
         <f>'Income Statement'!E19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="26">
         <f>'Income Statement'!F19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="26">
         <f>'Income Statement'!G19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="26">
         <f>'Income Statement'!H19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="26">
         <f>'Income Statement'!I19/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>DPS declared (SAR)</t>
         </is>
@@ -3046,380 +3041,380 @@
       <c r="D7" s="7" t="n">
         <v>2.2</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <f>Assumptions!D26</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="29">
         <f>Assumptions!E26</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="29">
         <f>Assumptions!F26</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <f>Assumptions!G26</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Book value / share (SAR)</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <f>'Balance Sheet'!B14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <f>'Balance Sheet'!C14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <f>'Balance Sheet'!D14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <f>'Balance Sheet'!E14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <f>'Balance Sheet'!F14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="26">
         <f>'Balance Sheet'!G14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <f>'Balance Sheet'!H14/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="26">
         <f>'Balance Sheet'!I14/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>P/E at spot (×)f</t>
         </is>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!B19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!C19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!D19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!E19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!F19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!G19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!H19/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="33">
         <f>Assumptions!$B$5/('Income Statement'!I19/Assumptions!$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>P/B at spot (×)f</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!B14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!C14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!D14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!E14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!F14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!G14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!H14/Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!I14/Assumptions!$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Dividend yield at spot (declared)</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <f>B7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <f>C7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="18">
         <f>D7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="18">
         <f>E7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="18">
         <f>F7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="18">
         <f>G7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <f>H7/Assumptions!$B$5</f>
         <v/>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="18">
         <f>I7/Assumptions!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Payout (of attributable NP)f</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <f>B7*Assumptions!$B$6/'Income Statement'!B19</f>
         <v/>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <f>C7*Assumptions!$B$6/'Income Statement'!C19</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="18">
         <f>D7*Assumptions!$B$6/'Income Statement'!D19</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <f>E7*Assumptions!$B$6/'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <f>F7*Assumptions!$B$6/'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <f>G7*Assumptions!$B$6/'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <f>H7*Assumptions!$B$6/'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="18">
         <f>I7*Assumptions!$B$6/'Income Statement'!I19</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <f>'Income Statement'!B9/'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <f>'Income Statement'!C9/'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="18">
         <f>'Income Statement'!D9/'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="18">
         <f>'Income Statement'!E9/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="18">
         <f>'Income Statement'!F9/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <f>'Income Statement'!G9/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="18">
         <f>'Income Statement'!H9/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="18">
         <f>'Income Statement'!I9/'Income Statement'!I6</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>'Income Statement'!B19/'Income Statement'!B6</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <f>'Income Statement'!C19/'Income Statement'!C6</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="18">
         <f>'Income Statement'!D19/'Income Statement'!D6</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <f>'Income Statement'!E19/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="18">
         <f>'Income Statement'!F19/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <f>'Income Statement'!G19/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="18">
         <f>'Income Statement'!H19/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="18">
         <f>'Income Statement'!I19/'Income Statement'!I6</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>ROAE (attributable)</t>
         </is>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <f>'Income Statement'!B19/'Balance Sheet'!B14</f>
         <v/>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <f>'Income Statement'!C19/'Balance Sheet'!C14</f>
         <v/>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="18">
         <f>'Income Statement'!D19/'Balance Sheet'!D14</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="18">
         <f>'Income Statement'!E19/'Balance Sheet'!E14</f>
         <v/>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <f>'Income Statement'!F19/'Balance Sheet'!F14</f>
         <v/>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <f>'Income Statement'!G19/'Balance Sheet'!G14</f>
         <v/>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <f>'Income Statement'!H19/'Balance Sheet'!H14</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <f>'Income Statement'!I19/'Balance Sheet'!I14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Net debt (IR) / EBITDA (×)</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="33">
         <f>'Balance Sheet'!B24/'Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <f>'Balance Sheet'!C24/'Income Statement'!C9</f>
         <v/>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <f>'Balance Sheet'!D24/'Income Statement'!D9</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="33">
         <f>'Balance Sheet'!E24/'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="33">
         <f>'Balance Sheet'!F24/'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="33">
         <f>'Balance Sheet'!G24/'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <f>'Balance Sheet'!H24/'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="33">
         <f>'Balance Sheet'!I24/'Income Statement'!I9</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Capex intensity (% of revenue)</t>
         </is>
@@ -3433,120 +3428,120 @@
       <c r="D17" s="10" t="n">
         <v>0.152</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="18">
         <f>-'Cash Flow'!E10/'Income Statement'!E6</f>
         <v/>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="18">
         <f>-'Cash Flow'!F10/'Income Statement'!F6</f>
         <v/>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="18">
         <f>-'Cash Flow'!G10/'Income Statement'!G6</f>
         <v/>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="18">
         <f>-'Cash Flow'!H10/'Income Statement'!H6</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="18">
         <f>-'Cash Flow'!I10/'Income Statement'!I6</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>FCF yield at spot (forecast)</t>
         </is>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="18">
         <f>'Cash Flow'!E11/(Assumptions!$B$5*Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="18">
         <f>'Cash Flow'!F11/(Assumptions!$B$5*Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="18">
         <f>'Cash Flow'!G11/(Assumptions!$B$5*Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="18">
         <f>'Cash Flow'!H11/(Assumptions!$B$5*Assumptions!$B$6)</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="18">
         <f>'Cash Flow'!I11/(Assumptions!$B$5*Assumptions!$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Revenue YoY</t>
         </is>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="18">
         <f>'Income Statement'!C6/'Income Statement'!B6-1</f>
         <v/>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="18">
         <f>'Income Statement'!D6/'Income Statement'!C6-1</f>
         <v/>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="18">
         <f>'Income Statement'!E6/'Income Statement'!D6-1</f>
         <v/>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="18">
         <f>'Income Statement'!F6/'Income Statement'!E6-1</f>
         <v/>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <f>'Income Statement'!G6/'Income Statement'!F6-1</f>
         <v/>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="18">
         <f>'Income Statement'!H6/'Income Statement'!G6-1</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="18">
         <f>'Income Statement'!I6/'Income Statement'!H6-1</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>EPS YoY</t>
         </is>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="18">
         <f>('Income Statement'!C19/'Income Statement'!B19)-1</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="18">
         <f>('Income Statement'!D19/'Income Statement'!C19)-1</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="18">
         <f>('Income Statement'!E19/'Income Statement'!D19)-1</f>
         <v/>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="18">
         <f>('Income Statement'!F19/'Income Statement'!E19)-1</f>
         <v/>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <f>('Income Statement'!G19/'Income Statement'!F19)-1</f>
         <v/>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="18">
         <f>('Income Statement'!H19/'Income Statement'!G19)-1</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="18">
         <f>('Income Statement'!I19/'Income Statement'!H19)-1</f>
         <v/>
       </c>
@@ -3938,7 +3933,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Discounted cash flow</t>
         </is>
@@ -3946,21 +3941,21 @@
       <c r="B6" s="7" t="n">
         <v>37.4</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <f>'SOTP Bridge'!C13</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>THE CENTRAL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Dividend discount</t>
         </is>
@@ -3968,7 +3963,7 @@
       <c r="B7" s="7" t="n">
         <v>29.2</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <f>'SOTP Bridge'!C22</f>
         <v/>
       </c>
@@ -3982,7 +3977,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Enterprise multiple on own history</t>
         </is>
@@ -3990,7 +3985,7 @@
       <c r="B8" s="7" t="n">
         <v>45.7</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -4004,7 +3999,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Normalised earnings power</t>
         </is>
@@ -4012,7 +4007,7 @@
       <c r="B9" s="7" t="n">
         <v>36.8</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <f>'Relative &amp; Normalized'!C9</f>
         <v/>
       </c>
@@ -4026,7 +4021,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Book value per share — a DISCLOSED FLOOR, never weighted</t>
         </is>
@@ -4041,48 +4036,48 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>THE CENTRAL — the class primary, not an average of the rows above</t>
         </is>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <f>C6</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Published range — the span of the present-value reads</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="23" t="n">
         <v>37.37</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="23" t="n">
         <v>47.97</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Spot price (SAR)</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Assumptions!$B$5</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Central against spot</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <f>C12/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -4165,15 +4160,15 @@
           <t>FCFF DCF (primary)</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <f>Summary!B6</f>
         <v/>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <f>Summary!C6</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <f>Summary!D6</f>
         <v/>
       </c>
@@ -4184,15 +4179,15 @@
           <t>Dividend discount (policy lens)</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <f>Summary!B7</f>
         <v/>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <f>Summary!C7</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <f>Summary!D7</f>
         <v/>
       </c>
@@ -4203,15 +4198,15 @@
           <t>Relative (EV/EBITDA)</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <f>Summary!B8</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <f>Summary!C8</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <f>Summary!D8</f>
         <v/>
       </c>
@@ -4222,45 +4217,45 @@
           <t>Normalized earnings</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>Summary!B9</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <f>Summary!C9</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <f>Summary!D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Weighted central</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <f>Summary!B10</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <f>Summary!C10</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f>Summary!D10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>Assumptions!$B$5</f>
         <v/>
       </c>
@@ -4705,7 +4700,7 @@
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>14400</v>
+        <v>13232.64560847266</v>
       </c>
     </row>
     <row r="33">
@@ -4745,43 +4740,55 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>MONTE CARLO (YZ-HAR v2 — engine outputs on the Monte Carlo sheet)</t>
+          <t>THE PRICE MAP — the production engine, reproduced (outputs on the Monte Carlo sheet)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Anchor volatility (HAR forecast, annualized)</t>
+          <t>Forward volatility over three months (annualised)</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.1617</v>
+        <v>0.1653</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Projected from this stock’s own recent, medium and longer-run variation</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Secular drift (daily) — zero-drift class</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>0</v>
+          <t>Tail parameter and width calibration</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>15.0 / 1.056</t>
+        </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>International/GCC name: zero drift passed Step 0; secular drift failed (−4.8%)</t>
+          <t>The market panel’s fitted pair. Neither is quoted alone: they trade off, and the honest object is the cone they jointly produce</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Net factor drift per quarter (16-factor stack)</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.0072</v>
+          <t>Momentum lean applied over three months</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>0.002404</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Direction call UP (reading +0.30 against a 0.25 threshold); capped at the strength measured</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -4790,7 +4797,7 @@
           <t>Paths / seed</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>50,000 / 42</t>
         </is>
@@ -4804,7 +4811,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Driver \ year</t>
         </is>
@@ -5102,23 +5109,23 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>First-year scale onto the reviewed half (annualised)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>1.006082103803541</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>1</v>
+          <t>Gross margin (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0.485</v>
       </c>
     </row>
     <row r="56">
@@ -5511,7 +5518,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
@@ -5521,7 +5528,7 @@
           <t>Basis</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Value (SAR mn)</t>
         </is>
@@ -5538,7 +5545,7 @@
           <t>FCFF DCF (§1.1): Σ PV FCFF + PV terminal</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <f>DCF!B27</f>
         <v/>
       </c>
@@ -5554,7 +5561,7 @@
           <t>% of core EV</t>
         </is>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="31">
         <f>DCF!B28</f>
         <v/>
       </c>
@@ -5570,7 +5577,7 @@
           <t>43.06% DIIC/TAWAL at carrying value</t>
         </is>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="19">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
@@ -5586,7 +5593,7 @@
           <t>Market mark: 561mn sh × €3.50 × 4.40</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="19">
         <f>Assumptions!$B$21</f>
         <v/>
       </c>
@@ -5602,7 +5609,7 @@
           <t>Total debt 22,475 − core cash 15,412</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="19">
         <f>-Assumptions!$B$23</f>
         <v/>
       </c>
@@ -5618,43 +5625,43 @@
           <t>Book, 31-Mar-26</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="19">
         <f>-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <f>C6+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>DCF fair value per share (SAR)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <f>C12/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Upside / (downside) vs spot</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="33">
+      <c r="C14" s="32">
         <f>C13/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5667,28 +5674,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>DPS (SAR)</t>
         </is>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <f>Assumptions!D26</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <f>Assumptions!E26</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <f>Assumptions!F26</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="29">
         <f>Assumptions!G26</f>
         <v/>
       </c>
@@ -5699,78 +5706,78 @@
           <t>PV of DPS @ Ke</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <f>C17/(1+Assumptions!$B$13)^1</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>D17/(1+Assumptions!$B$13)^2</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <f>E17/(1+Assumptions!$B$13)^3</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <f>F17/(1+Assumptions!$B$13)^4</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="26">
         <f>G17/(1+Assumptions!$B$13)^5</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Σ PV of explicit DPS (FY26–30E)</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <f>SUM(C18:G18)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Terminal value = DPS30 × (1+g) / (Ke − g)</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <f>G17*(1+Assumptions!$B$27)/(Assumptions!$B$13-Assumptions!$B$27)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <f>C20/(1+Assumptions!$B$13)^5</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DDM fair value per share (SAR)</t>
         </is>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <f>C19+C21</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  terminal as % of DDM value (device A-7)</t>
         </is>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="18">
         <f>C21/C22</f>
         <v/>
       </c>
@@ -5875,7 +5882,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>stc</t>
         </is>
@@ -5889,29 +5896,29 @@
       <c r="D6" s="9" t="n">
         <v>51119.024</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <f>D6*(1+Assumptions!$C$54)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <f>E6*(1+Assumptions!$D$54)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <f>F6*(1+Assumptions!$E$54)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <f>G6*(1+Assumptions!$F$54)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="17">
         <f>H6*(1+Assumptions!$G$54)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Channels</t>
         </is>
@@ -5925,29 +5932,29 @@
       <c r="D7" s="9" t="n">
         <v>14085.195</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <f>D7*(1+Assumptions!$C$51)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>E7*(1+Assumptions!$D$51)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>F7*(1+Assumptions!$E$51)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <f>G7*(1+Assumptions!$F$51)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <f>H7*(1+Assumptions!$G$51)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Solutions</t>
         </is>
@@ -5961,29 +5968,29 @@
       <c r="D8" s="9" t="n">
         <v>12730.189</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>D8*(1+Assumptions!$C$46)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>E8*(1+Assumptions!$D$46)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f>F8*(1+Assumptions!$E$46)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <f>G8*(1+Assumptions!$F$46)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <f>H8*(1+Assumptions!$G$46)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>stc Kuwait</t>
         </is>
@@ -5997,29 +6004,29 @@
       <c r="D9" s="9" t="n">
         <v>4179.842</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <f>D9*(1+Assumptions!$C$52)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>E9*(1+Assumptions!$D$52)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <f>F9*(1+Assumptions!$E$52)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <f>G9*(1+Assumptions!$F$52)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="17">
         <f>H9*(1+Assumptions!$G$52)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>stc Bahrain</t>
         </is>
@@ -6033,29 +6040,29 @@
       <c r="D10" s="9" t="n">
         <v>1967.83</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <f>D10*(1+Assumptions!$C$53)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>E10*(1+Assumptions!$D$53)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f>F10*(1+Assumptions!$E$53)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <f>G10*(1+Assumptions!$F$53)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <f>H10*(1+Assumptions!$G$53)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Center 3</t>
         </is>
@@ -6069,29 +6076,29 @@
       <c r="D11" s="9" t="n">
         <v>1961.666</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>D11*(1+Assumptions!$C$47)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>E11*(1+Assumptions!$D$47)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>F11*(1+Assumptions!$E$47)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <f>G11*(1+Assumptions!$F$47)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <f>H11*(1+Assumptions!$G$47)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>stc Bank</t>
         </is>
@@ -6105,29 +6112,29 @@
       <c r="D12" s="9" t="n">
         <v>1401.027</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>D12*(1+Assumptions!$C$44)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>E12*(1+Assumptions!$D$44)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>F12*(1+Assumptions!$E$44)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <f>G12*(1+Assumptions!$F$44)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="17">
         <f>H12*(1+Assumptions!$G$44)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Sirar</t>
         </is>
@@ -6141,29 +6148,29 @@
       <c r="D13" s="9" t="n">
         <v>826.545</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <f>D13*(1+Assumptions!$C$43)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>E13*(1+Assumptions!$D$43)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <f>F13*(1+Assumptions!$E$43)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <f>G13*(1+Assumptions!$F$43)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <f>H13*(1+Assumptions!$G$43)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Specialized</t>
         </is>
@@ -6177,29 +6184,29 @@
       <c r="D14" s="9" t="n">
         <v>355.306</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <f>D14*(1+Assumptions!$C$45)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f>E14*(1+Assumptions!$D$45)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="17">
         <f>F14*(1+Assumptions!$E$45)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="17">
         <f>G14*(1+Assumptions!$F$45)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="17">
         <f>H14*(1+Assumptions!$G$45)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>iot2</t>
         </is>
@@ -6213,29 +6220,29 @@
       <c r="D15" s="9" t="n">
         <v>321.668</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <f>D15*(1+Assumptions!$C$48)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>E15*(1+Assumptions!$D$48)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <f>F15*(1+Assumptions!$E$48)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <f>G15*(1+Assumptions!$F$48)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="17">
         <f>H15*(1+Assumptions!$G$48)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>SCCC</t>
         </is>
@@ -6249,29 +6256,29 @@
       <c r="D16" s="9" t="n">
         <v>303.969</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <f>D16*(1+Assumptions!$C$49)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <f>E16*(1+Assumptions!$D$49)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="17">
         <f>F16*(1+Assumptions!$E$49)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="17">
         <f>G16*(1+Assumptions!$F$49)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="17">
         <f>H16*(1+Assumptions!$G$49)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Other operating segments</t>
         </is>
@@ -6285,29 +6292,29 @@
       <c r="D17" s="9" t="n">
         <v>65.059</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <f>D17*(1+Assumptions!$C$50)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <f>E17*(1+Assumptions!$D$50)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
         <v/>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <f>F17*(1+Assumptions!$E$50)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
         <v/>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="17">
         <f>G17*(1+Assumptions!$F$50)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
         <v/>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="17">
         <f>H17*(1+Assumptions!$G$50)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Gross segment revenue</t>
         </is>
@@ -6324,29 +6331,29 @@
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <f>SUM(E6:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <f>SUM(G6:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <f>SUM(H6:H17)</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <f>SUM(I6:I17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Eliminations / adjustments</t>
         </is>
@@ -6360,29 +6367,29 @@
       <c r="D19" s="9" t="n">
         <v>-11498.645</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <f>E18*Assumptions!$C$57</f>
         <v/>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <f>F18*Assumptions!$D$57</f>
         <v/>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <f>G18*Assumptions!$E$57</f>
         <v/>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="17">
         <f>H18*Assumptions!$F$57</f>
         <v/>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="17">
         <f>I18*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Group revenue</t>
         </is>
@@ -6399,29 +6406,29 @@
         <f>D18+D19</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <f>E18+E19</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="17">
         <f>G18+G19</f>
         <v/>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="17">
         <f>H18+H19</f>
         <v/>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <f>I18+I19</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Group EBITDA</t>
         </is>
@@ -6435,62 +6442,62 @@
       <c r="D22" s="9" t="n">
         <v>24469</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <f>E20*Assumptions!$C$58</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="17">
         <f>F20*Assumptions!$D$58</f>
         <v/>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="17">
         <f>G20*Assumptions!$E$58</f>
         <v/>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="17">
         <f>H20*Assumptions!$F$58</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="17">
         <f>I20*Assumptions!$G$58</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <f>B22/B20</f>
         <v/>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="18">
         <f>C22/C20</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="18">
         <f>D22/D20</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="18">
         <f>E22/E20</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="18">
         <f>F22/F20</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <f>G22/G20</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <f>H22/H20</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="18">
         <f>I22/I20</f>
         <v/>
       </c>
@@ -6563,7 +6570,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Relative EV/EBITDA</t>
         </is>
@@ -6573,35 +6580,35 @@
           <t>FY26E EBITDA × justified multiple + stakes − net debt − NCI, /sh</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <f>(DCF!B7*Assumptions!$B$30+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23)*(1-Assumptions!$B$28)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  implied P/E cross-check at that value</t>
         </is>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="33">
         <f>C6*Assumptions!$B$6/Assumptions!$B$31</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  IS-build FY26E EPS, for reference</t>
         </is>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <f>'Income Statement'!E21</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Normalized earnings power</t>
         </is>
@@ -6611,29 +6618,29 @@
           <t>Normalized PAT (ex one-offs) × through-cycle P/E, /sh</t>
         </is>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <f>Assumptions!$B$32*Assumptions!$B$33/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  normalized EPS (SAR)</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <f>Assumptions!$B$32/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>P/B cross-check: spot / FY25 BVPS</t>
         </is>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <f>Assumptions!$B$5/('Balance Sheet'!D14/Assumptions!$B$6)</f>
         <v/>
       </c>
@@ -6723,23 +6730,23 @@
           <t>Group revenue</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <f>Segments!E20</f>
         <v/>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <f>Segments!F20</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <f>Segments!G20</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f>Segments!H20</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <f>Segments!I20</f>
         <v/>
       </c>
@@ -6750,23 +6757,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f>Segments!E22</f>
         <v/>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="19">
         <f>Segments!F22</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <f>Segments!G22</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <f>Segments!H22</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <f>Segments!I22</f>
         <v/>
       </c>
@@ -6777,23 +6784,23 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <f>-B6*Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <f>-C6*Assumptions!$D$59</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>-D6*Assumptions!$E$59</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <f>-E6*Assumptions!$F$59</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>-F6*Assumptions!$G$59</f>
         <v/>
       </c>
@@ -6804,23 +6811,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <f>B7+B8</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>F7+F8</f>
         <v/>
       </c>
@@ -6831,23 +6838,23 @@
           <t>NOPAT = EBIT × (1 − zakat/tax)</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <f>B9*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <f>C9*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>D9*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <f>E9*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>F9*(1-Assumptions!$B$7)</f>
         <v/>
       </c>
@@ -6858,23 +6865,23 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>-F8</f>
         <v/>
       </c>
@@ -6885,23 +6892,23 @@
           <t>− Capex</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <f>-B6*Assumptions!$C$60</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <f>-C6*Assumptions!$D$60</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>-D6*Assumptions!$E$60</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <f>-E6*Assumptions!$F$60</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>-F6*Assumptions!$G$60</f>
         <v/>
       </c>
@@ -6912,50 +6919,50 @@
           <t>− Increase in net working capital</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <f>-B6*Assumptions!$C$61</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <f>-C6*Assumptions!$D$61</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f>-D6*Assumptions!$E$61</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <f>-E6*Assumptions!$F$61</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>-F6*Assumptions!$G$61</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <f>SUM(B10:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <f>SUM(C10:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <f>SUM(D10:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f>SUM(E10:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f>SUM(F10:F13)</f>
         <v/>
       </c>
@@ -6966,61 +6973,61 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <f>1/(1+Assumptions!$B$17)^1</f>
         <v/>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="21">
         <f>1/(1+Assumptions!$B$17)^2</f>
         <v/>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <f>1/(1+Assumptions!$B$17)^3</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <f>1/(1+Assumptions!$B$17)^4</f>
         <v/>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <f>1/(1+Assumptions!$B$17)^5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <f>B14*B15</f>
         <v/>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <f>C14*C15</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <f>D14*D15</f>
         <v/>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E14*E15</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f>F14*F15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Σ PV of explicit FCFF (FY26–30E)</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <f>SUM(B16:F16)</f>
         <v/>
       </c>
@@ -7031,7 +7038,7 @@
           <t>Terminal NOPAT</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="17" t="n">
         <v>15445.66512484251</v>
       </c>
     </row>
@@ -7041,7 +7048,7 @@
           <t>+ book depreciation added back</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="17" t="n">
         <v>11436.60312602409</v>
       </c>
     </row>
@@ -7051,7 +7058,7 @@
           <t>- maintenance at current cost (disclosed life 15.23 years)</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="17" t="n">
         <v>-15461.02067352931</v>
       </c>
     </row>
@@ -7061,7 +7068,7 @@
           <t>- capital that real growth needs</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7071,17 +7078,17 @@
           <t>- inflation on working capital</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="17" t="n">
         <v>-271.10088</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Terminal free cash flow</t>
         </is>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <f>SUM(B19:B23)</f>
         <v/>
       </c>
@@ -7092,7 +7099,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <f>B24*(1+Assumptions!$B$18)/(Assumptions!$B$17-Assumptions!$B$18)</f>
         <v/>
       </c>
@@ -7103,29 +7110,29 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="17">
         <f>B25*F15</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Enterprise value — core operations</t>
         </is>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <f>B18+B26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>% terminal of EV (device A-7)</t>
         </is>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <f>B26/B27</f>
         <v/>
       </c>
@@ -7136,7 +7143,7 @@
           <t>+ Investments in associates (DIIC/TAWAL 43.06%)</t>
         </is>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="17">
         <f>Assumptions!$B$20</f>
         <v/>
       </c>
@@ -7147,7 +7154,7 @@
           <t>+ Telefónica 9.97% (market mark)</t>
         </is>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="17">
         <f>Assumptions!$B$21</f>
         <v/>
       </c>
@@ -7158,7 +7165,7 @@
           <t>− Net debt (IR basis, Q1-26)</t>
         </is>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="17">
         <f>-Assumptions!$B$23</f>
         <v/>
       </c>
@@ -7169,7 +7176,7 @@
           <t>− Non-controlling interests</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <f>-Assumptions!$B$24</f>
         <v/>
       </c>
@@ -7180,29 +7187,29 @@
           <t>+ Investment funds and unlisted equity investments</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <f>Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="20">
         <f>B27+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>DCF fair value per share (SAR)</t>
         </is>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <f>B34/Assumptions!$B$6</f>
         <v/>
       </c>
@@ -7213,7 +7220,7 @@
           <t>Upside / (downside) vs spot</t>
         </is>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="18">
         <f>B35/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -7318,37 +7325,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="24" t="n">
         <v>71777</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="24" t="n">
         <v>75893</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>77819</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="25">
         <f>Segments!E20</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="25">
         <f>Segments!F20</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="25">
         <f>Segments!G20</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="25">
         <f>Segments!H20</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="25">
         <f>Segments!I20</f>
         <v/>
       </c>
@@ -7368,24 +7375,24 @@
       <c r="D7" s="9" t="n">
         <v>37700</v>
       </c>
-      <c r="E7" s="18">
-        <f>E6*0.485</f>
-        <v/>
-      </c>
-      <c r="F7" s="18">
-        <f>F6*0.485</f>
-        <v/>
-      </c>
-      <c r="G7" s="18">
-        <f>G6*0.485</f>
-        <v/>
-      </c>
-      <c r="H7" s="18">
-        <f>H6*0.485</f>
-        <v/>
-      </c>
-      <c r="I7" s="18">
-        <f>I6*0.485</f>
+      <c r="E7" s="17">
+        <f>E6*Assumptions!$C$55</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>F6*Assumptions!$D$55</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>G6*Assumptions!$E$55</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>H6*Assumptions!$F$55</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>I6*Assumptions!$G$55</f>
         <v/>
       </c>
     </row>
@@ -7395,71 +7402,71 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <f>B7/B6</f>
         <v/>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <f>C7/C6</f>
         <v/>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="18">
         <f>D7/D6</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="18">
         <f>E7/E6</f>
         <v/>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="18">
         <f>F7/F6</f>
         <v/>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <f>G7/G6</f>
         <v/>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <f>H7/H6</f>
         <v/>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="18">
         <f>I7/I6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="24" t="n">
         <v>22445</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="24" t="n">
         <v>23951</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>24469</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="25">
         <f>Segments!E22</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <f>Segments!F22</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <f>Segments!G22</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="25">
         <f>Segments!H22</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="25">
         <f>Segments!I22</f>
         <v/>
       </c>
@@ -7470,35 +7477,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <f>B9/B6</f>
         <v/>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <f>C9/C6</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="18">
         <f>D9/D6</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <f>E9/E6</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="18">
         <f>F9/F6</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="18">
         <f>G9/G6</f>
         <v/>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <f>H9/H6</f>
         <v/>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="18">
         <f>I9/I6</f>
         <v/>
       </c>
@@ -7518,59 +7525,59 @@
       <c r="D11" s="9" t="n">
         <v>-10031</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>-E6*Assumptions!$C$59</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>-F6*Assumptions!$D$59</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>-G6*Assumptions!$E$59</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <f>-H6*Assumptions!$F$59</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <f>-I6*Assumptions!$G$59</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Operating profit (EBIT)</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="24" t="n">
         <v>13161</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="24" t="n">
         <v>14426</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>14438</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f>E9+E11</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <f>F9+F11</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="20">
         <f>G9+G11</f>
         <v/>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <f>H9+H11</f>
         <v/>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="20">
         <f>I9+I11</f>
         <v/>
       </c>
@@ -7578,71 +7585,71 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Share of associates &amp; JVs + net finance &amp; other</t>
+          <t>Associates, net finance, impairments &amp; other</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>1461</v>
+        <v>826</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>899</v>
+        <v>-2292</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>285</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <f>Assumptions!$C$62+Assumptions!$C$63+Assumptions!$C$64</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>Assumptions!$D$62+Assumptions!$D$63+Assumptions!$D$64</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <f>Assumptions!$E$62+Assumptions!$E$63+Assumptions!$E$64</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <f>Assumptions!$F$62+Assumptions!$F$63+Assumptions!$F$64</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <f>Assumptions!$G$62+Assumptions!$G$63+Assumptions!$G$64</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Profit before zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
-        <v>14622</v>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>15325</v>
-      </c>
-      <c r="D14" s="21" t="n">
+      <c r="B14" s="9" t="n">
+        <v>13987</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>12134</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>14723</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="20">
         <f>G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <f>H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <f>I12+I13</f>
         <v/>
       </c>
@@ -7662,59 +7669,59 @@
       <c r="D15" s="9" t="n">
         <v>466</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <f>-E14*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>-F14*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <f>-G14*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <f>-H14*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="17">
         <f>-I14*Assumptions!$B$7</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Profit from continuing operations</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="20" t="n">
         <v>12660</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="20" t="n">
         <v>10942</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="20" t="n">
         <v>15189</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="20">
         <f>G14+G15</f>
         <v/>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <f>H14+H15</f>
         <v/>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <f>I14+I15</f>
         <v/>
       </c>
@@ -7734,23 +7741,23 @@
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="17">
         <f>0</f>
         <v/>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="17">
         <f>0</f>
         <v/>
       </c>
@@ -7770,59 +7777,59 @@
       <c r="D18" s="9" t="n">
         <v>-361</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <f>-(E16)*0.020206295602669237</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <f>-(F16)*0.020206295602669237</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <f>-(G16)*0.020206295602669237</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <f>-(H16)*0.020206295602669237</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <f>-(I16)*0.020206295602669237</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Net profit (attributable)</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="24" t="n">
         <v>13295</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="24" t="n">
         <v>24689</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>14828</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <f>E16+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <f>F16+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="20">
         <f>G16+G17+G18</f>
         <v/>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <f>H16+H17+H18</f>
         <v/>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="20">
         <f>I16+I17+I18</f>
         <v/>
       </c>
@@ -7833,35 +7840,35 @@
           <t>Net margin (attributable)</t>
         </is>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="18">
         <f>B19/B6</f>
         <v/>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="18">
         <f>C19/C6</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="18">
         <f>D19/D6</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="18">
         <f>E19/E6</f>
         <v/>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="18">
         <f>F19/F6</f>
         <v/>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <f>G19/G6</f>
         <v/>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="18">
         <f>H19/H6</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="18">
         <f>I19/I6</f>
         <v/>
       </c>
@@ -7872,35 +7879,35 @@
           <t>EPS (SAR)</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <f>B19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <f>C19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <f>D19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="26">
         <f>E19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="26">
         <f>F19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="26">
         <f>G19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="26">
         <f>H19/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <f>I19/Assumptions!$B$6</f>
         <v/>
       </c>

--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -3942,7 +3942,7 @@
         <v>37.4</v>
       </c>
       <c r="C6" s="29">
-        <f>'SOTP Bridge'!C13</f>
+        <f>'SOTP Bridge'!C14</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
@@ -3964,7 +3964,7 @@
         <v>29.2</v>
       </c>
       <c r="C7" s="29">
-        <f>'SOTP Bridge'!C22</f>
+        <f>'SOTP Bridge'!C23</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
@@ -5109,23 +5109,23 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Gross margin (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="F55" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="G55" s="10" t="n">
-        <v>0.485</v>
+          <t>First-year scale onto the reviewed half (annualised)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>1.006082103803541</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -5368,6 +5368,28 @@
       </c>
       <c r="G66" s="7" t="n">
         <v>2.55</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gross margin (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>0.485</v>
       </c>
     </row>
     <row r="84">
@@ -5485,7 +5507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5553,12 +5575,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which terminal value (device A-7)</t>
+          <t xml:space="preserve">  of which terminal value</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>% of core EV</t>
+          <t>% of core enterprise value</t>
         </is>
       </c>
       <c r="C7" s="31">
@@ -5590,7 +5612,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Market mark: 561mn sh × €3.50 × 4.40</t>
+          <t>Market mark on the disclosed stake</t>
         </is>
       </c>
       <c r="C9" s="19">
@@ -5601,191 +5623,207 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>− Net debt (IR basis, Q1-26)</t>
+          <t>+ Investment funds and unlisted equity investments</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Total debt 22,475 − core cash 15,412</t>
+          <t>At fair value</t>
         </is>
       </c>
       <c r="C10" s="19">
-        <f>-Assumptions!$B$23</f>
+        <f>Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>− Net debt</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Total borrowings less cash, on the 30 June 2026 reviewed sheet</t>
+        </is>
+      </c>
+      <c r="C11" s="19">
+        <f>-Assumptions!$B$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>− Non-controlling interests</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Book, 31-Mar-26</t>
-        </is>
-      </c>
-      <c r="C11" s="19">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>At the minority’s share of equity value, not at book</t>
+        </is>
+      </c>
+      <c r="C12" s="19">
         <f>-Assumptions!$B$24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="25">
-        <f>C6+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>DCF fair value per share (SAR)</t>
+          <t>Equity value</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="30">
-        <f>C12/Assumptions!$B$6</f>
+      <c r="C13" s="25">
+        <f>C6+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23-Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
+          <t>DCF fair value per share (SAR)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="30">
+        <f>C13/Assumptions!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
           <t>Upside / (downside) vs spot</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="32">
-        <f>C13/Assumptions!$B$5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="32">
+        <f>C14/Assumptions!$B$5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>DDM — the locked dividend policy as a lens</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>DPS (SAR)</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D18" s="29">
         <f>Assumptions!D26</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E18" s="29">
         <f>Assumptions!E26</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F18" s="29">
         <f>Assumptions!F26</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G18" s="29">
         <f>Assumptions!G26</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>PV of DPS @ Ke</t>
         </is>
       </c>
-      <c r="C18" s="26">
-        <f>C17/(1+Assumptions!$B$13)^1</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>D17/(1+Assumptions!$B$13)^2</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
-        <f>E17/(1+Assumptions!$B$13)^3</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>F17/(1+Assumptions!$B$13)^4</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>G17/(1+Assumptions!$B$13)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Σ PV of explicit DPS (FY26–30E)</t>
-        </is>
-      </c>
       <c r="C19" s="26">
-        <f>SUM(C18:G18)</f>
+        <f>C18/(1+Assumptions!$B$13)^1</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>D18/(1+Assumptions!$B$13)^2</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>E18/(1+Assumptions!$B$13)^3</f>
+        <v/>
+      </c>
+      <c r="F19" s="26">
+        <f>F18/(1+Assumptions!$B$13)^4</f>
+        <v/>
+      </c>
+      <c r="G19" s="26">
+        <f>G18/(1+Assumptions!$B$13)^5</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Terminal value = DPS30 × (1+g) / (Ke − g)</t>
+          <t>Σ PV of explicit DPS (FY26–30E)</t>
         </is>
       </c>
       <c r="C20" s="26">
-        <f>G17*(1+Assumptions!$B$27)/(Assumptions!$B$13-Assumptions!$B$27)</f>
+        <f>SUM(C19:G19)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
+          <t>Terminal value = DPS30 × (1+g) / (Ke − g)</t>
+        </is>
+      </c>
+      <c r="C21" s="26">
+        <f>G18*(1+Assumptions!$B$27)/(Assumptions!$B$13-Assumptions!$B$27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C21" s="26">
-        <f>C20/(1+Assumptions!$B$13)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="C22" s="26">
+        <f>C21/(1+Assumptions!$B$13)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>DDM fair value per share (SAR)</t>
         </is>
       </c>
-      <c r="C22" s="23">
-        <f>C19+C21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  terminal as % of DDM value (device A-7)</t>
-        </is>
-      </c>
-      <c r="C23" s="18">
-        <f>C21/C22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Market-implied read: at spot, the market pays ≈ core EV of SAR 209bn for operations that produce ~SAR 10–11bn of model FCFF — an implied core FCFF yield of ~5% against a 7.6% WACC, i.e. the market already prices a large share of the terminal growth. The regular dividend (SAR 2.20 ≈ 5.0% yield) is ~0.9–1.0× covered by model FY26E FCF at the guided capex band — the balance sheet (SAR 15.4bn core cash) carries the difference; §1.7 of the study sensitizes this in real units.</t>
+      <c r="C23" s="23">
+        <f>C20+C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  terminal as a share of the dividend-model value</t>
+        </is>
+      </c>
+      <c r="C24" s="18">
+        <f>C22/C23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>What the market is paying, read off this sheet: at the spot price the market values the whole equity above what these lines add to, and the difference is the disagreement section 4 of the study takes apart. The regular dividend is covered 1.05 to 1.24 times by first-year model free cash flow across the range of capital intensity this company own three filed years actually ran — covered throughout that range, so the question is whether the data-centre build takes intensity above anything it has yet run.</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7167,7 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>% terminal of EV (device A-7)</t>
+          <t>% terminal of enterprise value</t>
         </is>
       </c>
       <c r="B28" s="22">
@@ -7162,7 +7200,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>− Net debt (IR basis, Q1-26)</t>
+          <t>− Net debt, on the 30 June 2026 reviewed sheet</t>
         </is>
       </c>
       <c r="B31" s="17">
@@ -7228,7 +7266,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>WACC is built on Assumptions as Ke = rf + β×ERP blended with after-tax Kd (§3.5-G); the alternative CDS-based WACC is on Assumptions row 88. Terminal value is disclosed as % of EV above rather than blended away (device A-7).</t>
+          <t>WACC is built on Assumptions as Ke = rf + β×ERP blended with after-tax Kd (§3.5-G); the alternative CDS-based WACC is on Assumptions row 88. Terminal value is disclosed as a share of enterprise value above rather than blended away.</t>
         </is>
       </c>
     </row>
@@ -7376,23 +7414,23 @@
         <v>37700</v>
       </c>
       <c r="E7" s="17">
-        <f>E6*Assumptions!$C$55</f>
+        <f>E6*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>F6*Assumptions!$D$55</f>
+        <f>F6*Assumptions!$D$68</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>G6*Assumptions!$E$55</f>
+        <f>G6*Assumptions!$E$68</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>H6*Assumptions!$F$55</f>
+        <f>H6*Assumptions!$F$68</f>
         <v/>
       </c>
       <c r="I7" s="17">
-        <f>I6*Assumptions!$G$55</f>
+        <f>I6*Assumptions!$G$68</f>
         <v/>
       </c>
     </row>

--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -4157,7 +4157,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>FCFF DCF (primary)</t>
+          <t>Cash-flow model (the class primary)</t>
         </is>
       </c>
       <c r="B6" s="29">
@@ -4176,7 +4176,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Dividend discount (policy lens)</t>
+          <t>Dividend discount</t>
         </is>
       </c>
       <c r="B7" s="29">
@@ -4195,7 +4195,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Relative (EV/EBITDA)</t>
+          <t>Enterprise multiple on own history</t>
         </is>
       </c>
       <c r="B8" s="29">
@@ -4214,7 +4214,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Normalized earnings</t>
+          <t>Normalised earnings power</t>
         </is>
       </c>
       <c r="B9" s="29">
@@ -4233,7 +4233,7 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Weighted central</t>
+          <t>Book value — a disclosed floor, never weighted into an answer</t>
         </is>
       </c>
       <c r="B10" s="30">

--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -654,43 +654,52 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Currency. SAR million unless stated. Spot SAR 43.58 (7 Jul 2026 close, from the attached daily history).</t>
+          <t>Currency. SAR million unless stated. Spot SAR 43.86 (3 September 2026 close, the latest known price this study is
+ struck against; the Monte Carlo cone starts at the last session in the price library, 31 August 2026, which is a
+ different date and is stated as one).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Historical financials are stc’s own IR disclosure (FY23–FY25 releases, restated continuing-ops basis;</t>
+          <t>Historical financials are the company’s own audited annual and reviewed interim statements, FY2023</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Q1-26 release 28 Apr 2026); balance-sheet detail from the Q1-2026 interim FS (31-Dec-25 comparatives).</t>
+          <t>onward, each fetched from its own investor-relations archive and listed with that URL in the study’s</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>bibliography. The balance sheet the bridge stands on is the reviewed interim to 30 June 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Sheets: Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized ·</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity ·</t>
+          <t>Sheets: Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized ·</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Per-Share &amp; Ratios · Peer &amp; Sector.</t>
         </is>
@@ -741,7 +750,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>FY23–FY25 grouped from stc disclosure to a house layout (blue; FY25 detail from the Q1-2026 FS comparatives). Forecast rolls forward clean-surplus; the check row is zero by construction.</t>
+          <t>FY23–FY25 grouped from the company's own statements into one layout (blue). Forecast rolls forward clean-surplus; the check row is zero by construction.</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1437,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Historic mapping: FY25 line detail from the Q1-2026 FS 31-Dec-25 comparatives (PP&amp;E 95,313 + ROU 2,635 + intangibles 28,139 + inv. property 350 grouped; cash 13,376 + murabaha 1,732). FY23/FY24 detail lines are grouped estimates reconciling to the disclosed IR totals (blue totals are as-disclosed); "Other" lines are the disclosed-total balancing items, shown as formulas. FY26E borrowings step up SAR +7,284mn = the Jan-2026 $2bn sukuk (net of FY26 amortisation) — thereafter gross debt held flat. Two cash framings exist (FS 21,442 incl. stc bank vs IR 15,412 core): the model rolls the FS-basis cash from FY25’s 15,108 (cash + murabaha) and states the IR basis in the net-debt memo.</t>
+          <t>Historic mapping: the FY2025 line detail is grouped from that year's own audited statements (property and equipment, right-of-use assets, intangibles and investment property into one line; cash and short-term murabahas into another). FY23/FY24 detail lines are groupings that reconcile to the disclosed totals (blue totals are as disclosed); "Other" lines are the balancing items against those totals, shown as formulas so a reader can see them close. FY26E borrowings step up SAR +7,284mn = the Jan-2026 $2bn sukuk (net of FY26 amortisation) — thereafter gross debt held flat. Two cash framings exist (FS 21,442 incl. stc bank vs IR 15,412 core): the model rolls the FS-basis cash from FY25’s 15,108 (cash + murabaha) and states the IR basis in the net-debt memo.</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2257,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monte Carlo — engine outputs (YZ-HAR v2)</t>
+          <t>Monte Carlo — the price cone as the engine struck it</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2262,7 +2271,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>50,000 paths · 16 factors · seed 42 · computed by the Testahil MC engine (values, not a sheet simulation). Zero drift — the Step 0-passed configuration for this name.</t>
+          <t>50,000 paths, seed 42, computed by the engine itself rather than simulated in this sheet. The distribution carries a live momentum lean, upward, worth 0.13% at one month and 0.24% at three.</t>
         </is>
       </c>
     </row>
@@ -2750,14 +2759,14 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>The WACC axis centres on the sourced bottom-up build (rf 5.5% + β 0.48 × ERP 5.01%, blended with after-tax Kd 4.5%); the CDS-ERP alternative WACC (7.90%) sits between rows 3 and 4. At β = 1.0 the WACC is 9.90% — off this grid deliberately: see the beta grid below.</t>
+          <t>The cost-of-capital axis centres on the sourced bottom-up build — a normalised risk-free rate of 4.54% plus a beta of 0.7078 times the 5.72% premium this study names as central, blended with an after-tax cost of debt of 3.89% at a 9.7% debt weight. On the alternative premium basis, published beside the central one rather than chosen silently, the same build gives 8.10%. At a beta of 1.00 the rate is 9.64%, which sits off this grid deliberately and is priced in the beta grid below.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Beta sensitivity (regressed β = 0.48 on a 9-week window — grid mandatory)</t>
+          <t>Beta sensitivity — the regression gives 0.7078 and the grid prices the answer either side of it</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2778,12 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Ke (rating ERP)</t>
+          <t>Cost of equity (central premium basis)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>Cost of capital</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -2802,7 +2811,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="B17" s="18">
         <f>Assumptions!$B$10+A17*Assumptions!$B$12</f>
@@ -2816,15 +2825,10 @@
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C17)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C17-Assumptions!$B$18)/(1+C17)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>&lt;- regressed base</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>0.7</v>
+        <v>0.7078292485042049</v>
       </c>
       <c r="B18" s="18">
         <f>Assumptions!$B$10+A18*Assumptions!$B$12</f>
@@ -2837,6 +2841,11 @@
       <c r="D18" s="26">
         <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C18)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C18-Assumptions!$B$18)/(1+C18)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
         <v/>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>&lt;- the adopted regression beta</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2874,7 +2883,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>&lt;- house fallback had the regression failed</t>
+          <t>&lt;- the fallback this desk would have used had the regression not been usable</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2933,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Per-share &amp; ratios — the standing dashboard (device A-5)</t>
+          <t>Per-share &amp; ratios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2940,7 +2949,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Links to statements / Assumptions.</t>
+          <t>Every line links to the statements and the assumptions behind them.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3856,13 +3865,6 @@
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Sector: KSA mobile ≈ 57/27/16 stc/Mobily/Zain; Nov-2024 CST spectrum auction (stc: 600MHz + 3.8GHz); 10,800+ stc 5G sites, 63% populated coverage; FTTH 3.75mn; FWA one of the highest-adoption markets globally; center3–HUMAIN 1GW AI-DC ambition; SilkLink Syria fibre corridor (SAR 3bn, Feb-2026). Peer P/E band 10.7–17.6×; stc premium tracks its share, balance sheet and yield.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Analyst context (not a model input): 17 analysts, 8 Buy / 9 Hold, average 12m TP SAR 47.9 (41.1–55.0), Jul-2026.</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3907,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Four-lens fair value vs spot. Base links live; bear/bull are scenario outputs (study §1.5).</t>
+          <t>The class primary is the central; the other lenses sit beside it as cross-checks and are never weighted into it. Base links live; bear and bull are the same model on one driver’s own filed range (study §1.5).</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5404,12 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>rf source</t>
+          <t>Risk-free rate — where the quote comes from</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Derived SAR 10Y sovereign: SRC (govt-guaranteed) $1.5bn 10y sukuk priced UST+95bp on 8-Jul-2026; UST 10Y 4.45% → 5.40% USD basis; the Saudi Exchange "KSA Sovereign Local Currency Debt Primer Update" (21-May-2026) documents SAR sovereign yields sitting ABOVE the USD curve through 10Y → 5.4–5.6% band, 5.5% point. Cross-check: FAB Securities stc note (27-Feb-2026) uses 5.5%. Per house rule the SAR-USD peg does NOT make UST a substitute — this is a documented named mistake in professional practice.</t>
+          <t>One dated sovereign quote is held for every Saudi company this desk covers, so no single study carries a rate of its own: 5.52% as at 2026-09-03, less this sovereign’s own default spread of 0.98%, giving the normalised 4.54% the cost of equity is built on. Country risk is then charged once, inside the equity risk premium, rather than twice. The Saudi sovereign quote on the house macro path carries an as-of date of 31 July 2026 and this schedule is struck on 5 September 2026, so it is 36 days old against the 14-day bound. It is accepted DELIBERATELY and the age is disclosed here rather than used quietly; refreshing the path is a macro-path task that moves every Saudi study at once, not a lever inside this one.</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5458,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Daily stc-vs-TASI OLS, n=40 paired sessions 5-May→7-Jul-2026 (TASI closes: investing.com historical table; stc: the attached price history): beta 0.475 (SE 0.189), R² 14.3%, alpha ≈ 0. Ex-Eid-gap robustness: 0.494. Passes RegressionBetaAttempt.is_usable() (n≥24, R²≥5%, SE&lt;|β|, β&gt;0). Honest flag: a 9-week daily window is the best obtainable (Yahoo/stooq/WSJ TASI history all blocked programmatically; Saudi Exchange login-gated); a 2–5yr weekly regression should replace it when accessible. Sensitivity: at β=1.0, Ke 10.51%, WACC 9.90% (rating basis) — the DCF grid in §1.9 spans this.</t>
+          <t>A 4.91-year weekly regression of stc against the published index of the exchange it is listed on, the Tadawul All Share Index, read as of 2026-08-18: 252 paired weeks on that exchange’s own trading week, beta 0.7078, standard error 0.1029, R² 30.2%, and a confidence interval running 0.5386 to 0.8771. It is the first tier of the house preference order rather than a stopgap. A superseded reading of 0.4800, taken from a nine-week daily window on a commercial vendor’s index quotes, is recorded in the bibliography and is not used. Sensitivity: at a beta of 1.00 the cost of equity is 10.26% and the cost of capital 9.64%, which the beta grid on the Sensitivity sheet prices in full.</t>
         </is>
       </c>
     </row>
@@ -5480,19 +5482,19 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Market cap = 43.58 × 4,989.8mn = SAR 217,455mn; total debt = SAR 22,475mn (Q1-2026 IR release, post the Jan-2026 $2bn sukuk; excludes lease liabilities 2,296). E/(D+E) = 90.6%.</t>
+          <t>Market-value equity, never book: the latest known close of SAR 43.86 on 2026-09-03 times 4,993,024 thousand shares outstanding — issued capital of SAR 50,000,000 thousand in shares of SAR 10 each, which divides to the 5,000,000 thousand shares note 17 of the reviewed 30 June 2026 interim itself states, less 6,976 thousand held in treasury. Debt is the borrowings total from the LATEST DISCLOSED balance sheet, 30 June 2026, SAR 23,536,554 thousand, which reproduces from the same interim's own financing cash flows to twelve basis points. E/(D+E) = 90.3%.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Full reference &amp; cache</t>
+          <t>Both premium bases</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>See Cost_of_Capital_Reference.md (Saudi Arabia row, filled 09-07-2026) and wacc_builder.py for the standing method. Both ERP-basis WACCs are published per protocol.</t>
+          <t>The cost of capital is built the same way for every market this desk covers: the sovereign yield for the country, less that same sovereign’s own default spread so country risk is charged once rather than twice, plus beta times an equity risk premium published for Saudi Arabia specifically. Both premium bases are published — 5.72% central and 5.01% on the alternative — giving costs of capital of 8.13% and 8.10%, so the choice is visible rather than made silently.</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7955,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Sources: stc FY2024/FY2025 IR releases + Q1-2026 interim FS (all stc.com). FY23/FY24 restated to continuing operations (TAWAL + Digital Infrastructure Co reclassified as discontinued; FY24 discontinued profit 13,973 incl. the SAR 12,885mn disposal gain). One-offs: FY23 AlKhobar land gain +1,296, WHT reversal +724, ERP −863; FY24 WHT reversal +1,500, ERP −2,577, BGSM impairment −764; FY25 zakat credit +466, ERP ≈ −824. "Share of associates + net finance &amp; other" is the residual bridging disclosed EBIT to disclosed profit before zakat — stc does not publish those lines separately in the IR release layout; the FY25 annual FS carries the full detail.</t>
+          <t>Sources — the filings every figure above was read out of: audited consolidated financial statements for the year ended 31 December 2024; audited consolidated financial statements for the year ended 31 December 2025; reviewed condensed consolidated interim financial statements for the six months ended 30 June 2026; fourth-quarter and full-year 2025 earnings presentation; second-quarter and half-year 2026 earnings presentation — every one fetched from the company's own investor-relations archive. FY23/FY24 restated to continuing operations (TAWAL + Digital Infrastructure Co reclassified as discontinued; FY24 discontinued profit 13,973 incl. the SAR 12,885mn disposal gain). One-offs: FY23 AlKhobar land gain +1,296, WHT reversal +724, ERP −863; FY24 WHT reversal +1,500, ERP −2,577, BGSM impairment −764; FY25 zakat credit +466, ERP ≈ −824. "Share of associates + net finance &amp; other" is the residual bridging disclosed EBIT to disclosed profit before zakat — stc does not publish those lines separately in the IR release layout; the FY25 annual FS carries the full detail.</t>
         </is>
       </c>
     </row>

--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="C6" s="29">
         <f>'SOTP Bridge'!C14</f>
@@ -3985,14 +3985,14 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="C8" s="29">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
       <c r="D8" s="7" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>37.37</v>
+        <v>37.3</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>47.97</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="15">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>3927.589835802536</v>
+        <v>3921.206149602089</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>14450.68811216044</v>
+        <v>14503.30474307932</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
@@ -5181,19 +5181,19 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>0.319847256594818</v>
+        <v>0.3205740707168828</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.3190366010783908</v>
+        <v>0.3197807704348273</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.3184831288736253</v>
+        <v>0.319055773120738</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>0.3182052626065098</v>
+        <v>0.318382960635945</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0.3182052626065097</v>
+        <v>0.3177323370749691</v>
       </c>
     </row>
     <row r="59">
@@ -5825,7 +5825,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>What the market is paying, read off this sheet: at the spot price the market values the whole equity above what these lines add to, and the difference is the disagreement section 4 of the study takes apart. The regular dividend is covered 1.05 to 1.24 times by first-year model free cash flow across the range of capital intensity this company own three filed years actually ran — covered throughout that range, so the question is whether the data-centre build takes intensity above anything it has yet run.</t>
+          <t>What the market is paying, read off this sheet: at the spot price the market values the whole equity above what these lines add to, and the difference is the disagreement section 4 of the study takes apart. The regular dividend is covered 1.06 to 1.24 times by first-year model free cash flow across the range of capital intensity this company own three filed years actually ran — covered throughout that range, so the question is whether the data-centre build takes intensity above anything it has yet run.</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Operating segments — the eleven the company discloses</t>
+          <t>Operating segments — the 12 the company discloses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>15445.66512484251</v>
+        <v>15407.07760876889</v>
       </c>
     </row>
     <row r="20">

--- a/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
+++ b/engine/stc_study/STC_Valuation_Model_05092026_public.xlsx
@@ -800,39 +800,36 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Net fixed &amp; intangible assets (PP&amp;E, ROU, intangibles, inv. prop.)</t>
-        </is>
-      </c>
-      <c r="B6" s="17">
-        <f>B12-B7-B8-B9-B10-B11</f>
-        <v/>
-      </c>
-      <c r="C6" s="17">
-        <f>C12-C7-C8-C9-C10-C11</f>
-        <v/>
-      </c>
-      <c r="D6" s="17">
-        <f>D12-D7-D8-D9-D10-D11</f>
-        <v/>
+          <t>PP&amp;E, ROU, intangibles &amp; inv. property</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>92000</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>95500</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>126436</v>
       </c>
       <c r="E6" s="19">
-        <f>D6+Segments!E20*Assumptions!$C$60+'Income Statement'!E11</f>
+        <f>D6+Segments!E20*Assumptions!$C$62+'Income Statement'!E11</f>
         <v/>
       </c>
       <c r="F6" s="19">
-        <f>E6+Segments!F20*Assumptions!$D$60+'Income Statement'!F11</f>
+        <f>E6+Segments!F20*Assumptions!$D$62+'Income Statement'!F11</f>
         <v/>
       </c>
       <c r="G6" s="19">
-        <f>F6+Segments!G20*Assumptions!$E$60+'Income Statement'!G11</f>
+        <f>F6+Segments!G20*Assumptions!$E$62+'Income Statement'!G11</f>
         <v/>
       </c>
       <c r="H6" s="19">
-        <f>G6+Segments!H20*Assumptions!$F$60+'Income Statement'!H11</f>
+        <f>G6+Segments!H20*Assumptions!$F$62+'Income Statement'!H11</f>
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>H6+Segments!I20*Assumptions!$G$60+'Income Statement'!I11</f>
+        <f>H6+Segments!I20*Assumptions!$G$62+'Income Statement'!I11</f>
         <v/>
       </c>
     </row>
@@ -924,23 +921,23 @@
         <v>26727</v>
       </c>
       <c r="E9" s="19">
-        <f>D9+Segments!E20*Assumptions!$C$61</f>
+        <f>D9+Segments!E20*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F9" s="19">
-        <f>E9+Segments!F20*Assumptions!$D$61</f>
+        <f>E9+Segments!F20*Assumptions!$D$63</f>
         <v/>
       </c>
       <c r="G9" s="19">
-        <f>F9+Segments!G20*Assumptions!$E$61</f>
+        <f>F9+Segments!G20*Assumptions!$E$63</f>
         <v/>
       </c>
       <c r="H9" s="19">
-        <f>G9+Segments!H20*Assumptions!$F$61</f>
+        <f>G9+Segments!H20*Assumptions!$F$63</f>
         <v/>
       </c>
       <c r="I9" s="19">
-        <f>H9+Segments!I20*Assumptions!$G$61</f>
+        <f>H9+Segments!I20*Assumptions!$G$63</f>
         <v/>
       </c>
     </row>
@@ -957,26 +954,26 @@
         <v>30755</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>15080</v>
+        <v>15108</v>
       </c>
       <c r="E10" s="19">
-        <f>'Cash Flow'!E16</f>
+        <f>'Cash Flow'!E20</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>'Cash Flow'!F16</f>
+        <f>'Cash Flow'!F20</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>'Cash Flow'!G16</f>
+        <f>'Cash Flow'!G20</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>'Cash Flow'!H16</f>
+        <f>'Cash Flow'!H20</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>'Cash Flow'!I16</f>
+        <f>'Cash Flow'!I20</f>
         <v/>
       </c>
     </row>
@@ -986,11 +983,13 @@
           <t>Other assets</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>2600</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>2600</v>
+      <c r="B11" s="17">
+        <f>159646-B6-B7-B8-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>160638-C6-C7-C8-C9-C10</f>
+        <v/>
       </c>
       <c r="D11" s="9" t="n">
         <v>2952</v>
@@ -1028,26 +1027,27 @@
       <c r="C12" s="24" t="n">
         <v>160638</v>
       </c>
-      <c r="D12" s="24" t="n">
-        <v>157477</v>
-      </c>
-      <c r="E12" s="27">
+      <c r="D12" s="27">
+        <f>SUM(D6:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
         <f>SUM(E6:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="20">
         <f>SUM(F6:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="20">
         <f>SUM(G6:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="20">
         <f>SUM(H6:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="20">
         <f>SUM(I6:I11)</f>
         <v/>
       </c>
@@ -1068,23 +1068,23 @@
         <v>83414</v>
       </c>
       <c r="E14" s="19">
-        <f>D14+'Income Statement'!E19-Assumptions!$C$66*Assumptions!$B$6</f>
+        <f>D14+'Income Statement'!E19-Assumptions!$C$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F14" s="19">
-        <f>E14+'Income Statement'!F19-Assumptions!$D$66*Assumptions!$B$6</f>
+        <f>E14+'Income Statement'!F19-Assumptions!$D$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="G14" s="19">
-        <f>F14+'Income Statement'!G19-Assumptions!$E$66*Assumptions!$B$6</f>
+        <f>F14+'Income Statement'!G19-Assumptions!$E$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="H14" s="19">
-        <f>G14+'Income Statement'!H19-Assumptions!$F$66*Assumptions!$B$6</f>
+        <f>G14+'Income Statement'!H19-Assumptions!$F$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="I14" s="19">
-        <f>H14+'Income Statement'!I19-Assumptions!$G$66*Assumptions!$B$6</f>
+        <f>H14+'Income Statement'!I19-Assumptions!$G$68*Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>26500</v>
+        <v>27500</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>29610</v>
@@ -1278,16 +1278,15 @@
         </is>
       </c>
       <c r="B20" s="17">
-        <f>B12-B16-B17-B18-B19</f>
+        <f>159646-B16-B17-B18-B19</f>
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>C12-C16-C17-C18-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="17">
-        <f>D12-D16-D17-D18-D19</f>
-        <v/>
+        <f>160638-C16-C17-C18-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>14876</v>
       </c>
       <c r="E20" s="17">
         <f>D20</f>
@@ -1425,13 +1424,6 @@
       <c r="I24" s="17">
         <f>I17-I10</f>
         <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Historic mapping: disclosed IR anchors (total assets, cash+murabaha, total debt, attributable equity) are blue as reported; FY25 line detail (associates 4,641 · financial assets 24,893 · receivables 26,727 · leases 2,253 · payables+financial liabilities 29,610 · NCI 3,482) is from the Q1-2026 FS 31-Dec-25 comparatives; FY23/FY24 line detail is estimated to tie to the disclosed totals (flagged). "Net fixed &amp; intangible assets" and "Zakat payable, provisions &amp; other liabilities" are the balancing lines — shown as formulas off the disclosed totals, so the balance check is exact in every column. FY26E borrowings step up SAR +7,284mn (the completed Jan-2026 $2bn sukuk net of amortisation); gross debt flat thereafter. Two cash framings: FS cash incl. stc bank (21,442 at Q1-26) vs IR core-group cash (15,412) — the model rolls the IR-basis series (FY25: 15,080).</t>
-        </is>
       </c>
     </row>
     <row r="26">
@@ -1633,23 +1625,23 @@
         </is>
       </c>
       <c r="E10" s="19">
-        <f>-Segments!E20*Assumptions!$C$60</f>
+        <f>-Segments!E20*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="F10" s="19">
-        <f>-Segments!F20*Assumptions!$D$60</f>
+        <f>-Segments!F20*Assumptions!$D$62</f>
         <v/>
       </c>
       <c r="G10" s="19">
-        <f>-Segments!G20*Assumptions!$E$60</f>
+        <f>-Segments!G20*Assumptions!$E$62</f>
         <v/>
       </c>
       <c r="H10" s="19">
-        <f>-Segments!H20*Assumptions!$F$60</f>
+        <f>-Segments!H20*Assumptions!$F$62</f>
         <v/>
       </c>
       <c r="I10" s="19">
-        <f>-Segments!I20*Assumptions!$G$60</f>
+        <f>-Segments!I20*Assumptions!$G$62</f>
         <v/>
       </c>
     </row>
@@ -1714,23 +1706,23 @@
         </is>
       </c>
       <c r="E13" s="19">
-        <f>-Assumptions!$C$66*Assumptions!$B$6</f>
+        <f>-Assumptions!$C$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F13" s="19">
-        <f>-Assumptions!$D$66*Assumptions!$B$6</f>
+        <f>-Assumptions!$D$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="G13" s="19">
-        <f>-Assumptions!$E$66*Assumptions!$B$6</f>
+        <f>-Assumptions!$E$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="H13" s="19">
-        <f>-Assumptions!$F$66*Assumptions!$B$6</f>
+        <f>-Assumptions!$F$68*Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="I13" s="19">
-        <f>-Assumptions!$G$66*Assumptions!$B$6</f>
+        <f>-Assumptions!$G$68*Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2437,7 +2429,7 @@
         </is>
       </c>
       <c r="B18" s="31">
-        <f>Assumptions!$B$37</f>
+        <f>Assumptions!$B$39</f>
         <v/>
       </c>
     </row>
@@ -2448,7 +2440,7 @@
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Assumptions!$B$39</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
     </row>
@@ -2633,140 +2625,140 @@
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
-        <v>0.07132614912126105</v>
+        <v>0.07531054603967399</v>
       </c>
       <c r="B6" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A6-B$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A6-B$5)/(1+$A6)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A6-C$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A6-C$5)/(1+$A6)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A6-D$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A6-D$5)/(1+$A6)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A6-E$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A6-E$5)/(1+$A6)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A6-F$5)/(1+$A6)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A6)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A6-F$5)/(1+$A6)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="n">
-        <v>0.07632614912126104</v>
+        <v>0.08031054603967398</v>
       </c>
       <c r="B7" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A7-B$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A7-B$5)/(1+$A7)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A7-C$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A7-C$5)/(1+$A7)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A7-D$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A7-D$5)/(1+$A7)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A7-E$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A7-E$5)/(1+$A7)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A7-F$5)/(1+$A7)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A7)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A7-F$5)/(1+$A7)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="n">
-        <v>0.08132614912126104</v>
+        <v>0.08531054603967399</v>
       </c>
       <c r="B8" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A8-B$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A8-B$5)/(1+$A8)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A8-C$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A8-C$5)/(1+$A8)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A8-D$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A8-D$5)/(1+$A8)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A8-E$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A8-E$5)/(1+$A8)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A8-F$5)/(1+$A8)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A8)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A8-F$5)/(1+$A8)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="n">
-        <v>0.08632614912126105</v>
+        <v>0.09031054603967399</v>
       </c>
       <c r="B9" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A9-B$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A9-B$5)/(1+$A9)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A9-C$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A9-C$5)/(1+$A9)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A9-D$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A9-D$5)/(1+$A9)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A9-E$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A9-E$5)/(1+$A9)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A9-F$5)/(1+$A9)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A9)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A9-F$5)/(1+$A9)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n">
-        <v>0.09132614912126104</v>
+        <v>0.09531054603967398</v>
       </c>
       <c r="B10" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A10-B$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+B$5)/($A10-B$5)/(1+$A10)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C10" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A10-C$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+C$5)/($A10-C$5)/(1+$A10)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A10-D$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+D$5)/($A10-D$5)/(1+$A10)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A10-E$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+E$5)/($A10-E$5)/(1+$A10)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F10" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A10-F$5)/(1+$A10)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+$A10)^{1,2,3,4,5})+DCF!$F$14*(1+F$5)/($A10-F$5)/(1+$A10)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>The cost-of-capital axis centres on the sourced bottom-up build — a normalised risk-free rate of 4.54% plus a beta of 0.7078 times the 5.72% premium this study names as central, blended with an after-tax cost of debt of 3.89% at a 9.7% debt weight. On the alternative premium basis, published beside the central one rather than chosen silently, the same build gives 8.10%. At a beta of 1.00 the rate is 9.64%, which sits off this grid deliberately and is priced in the beta grid below.</t>
+          <t>The cost-of-capital axis centres on the sourced bottom-up build — a normalised risk-free rate of 4.54% plus a beta of 0.7093 times the 5.72% premium this study names as central, blended with an after-tax cost of debt of 3.89% at a 9.7% debt weight. On the alternative premium basis, published beside the central one rather than chosen silently, the same build gives 8.31%. At a beta of 1.00 the rate is 9.64%, which sits off this grid deliberately and is priced in the beta grid below.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Beta sensitivity — the regression gives 0.7078 and the grid prices the answer either side of it</t>
+          <t>Beta sensitivity — the regression gives 0.7093 and the grid prices the answer either side of it</t>
         </is>
       </c>
     </row>
@@ -2801,11 +2793,11 @@
         <v/>
       </c>
       <c r="C16" s="18">
-        <f>(1-Assumptions!$B$16)*B16+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B16+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D16" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C16)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C16-Assumptions!$B$18)/(1+C16)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C16)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C16-Assumptions!$B$20)/(1+C16)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2818,28 +2810,28 @@
         <v/>
       </c>
       <c r="C17" s="18">
-        <f>(1-Assumptions!$B$16)*B17+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B17+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D17" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C17)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C17-Assumptions!$B$18)/(1+C17)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C17)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C17-Assumptions!$B$20)/(1+C17)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>0.7078292485042049</v>
+        <v>0.7092581337669651</v>
       </c>
       <c r="B18" s="18">
         <f>Assumptions!$B$10+A18*Assumptions!$B$12</f>
         <v/>
       </c>
       <c r="C18" s="18">
-        <f>(1-Assumptions!$B$16)*B18+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B18+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D18" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C18)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C18-Assumptions!$B$18)/(1+C18)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C18)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C18-Assumptions!$B$20)/(1+C18)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2857,11 +2849,11 @@
         <v/>
       </c>
       <c r="C19" s="18">
-        <f>(1-Assumptions!$B$16)*B19+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B19+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D19" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C19)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C19-Assumptions!$B$18)/(1+C19)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C19)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C19-Assumptions!$B$20)/(1+C19)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -2874,11 +2866,11 @@
         <v/>
       </c>
       <c r="C20" s="18">
-        <f>(1-Assumptions!$B$16)*B20+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B20+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D20" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C20)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C20-Assumptions!$B$18)/(1+C20)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C20)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C20-Assumptions!$B$20)/(1+C20)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2896,11 +2888,11 @@
         <v/>
       </c>
       <c r="C21" s="18">
-        <f>(1-Assumptions!$B$16)*B21+Assumptions!$B$16*Assumptions!$B$15</f>
+        <f>(1-Assumptions!$B$18)*B21+Assumptions!$B$18*Assumptions!$B$17</f>
         <v/>
       </c>
       <c r="D21" s="26">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C21)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$18)/(C21-Assumptions!$B$18)/(1+C21)^5+Assumptions!$B$20+Assumptions!$B$21-Assumptions!$B$23-Assumptions!$B$24)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,1/(1+C21)^{1,2,3,4,5})+DCF!$F$14*(1+Assumptions!$B$20)/(C21-Assumptions!$B$20)/(1+C21)^5+Assumptions!$B$22+Assumptions!$B$23-Assumptions!$B$25-Assumptions!$B$26)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3051,23 +3043,23 @@
         <v>2.2</v>
       </c>
       <c r="E7" s="29">
-        <f>Assumptions!C26</f>
+        <f>Assumptions!C28</f>
         <v/>
       </c>
       <c r="F7" s="29">
-        <f>Assumptions!D26</f>
+        <f>Assumptions!D28</f>
         <v/>
       </c>
       <c r="G7" s="29">
-        <f>Assumptions!E26</f>
+        <f>Assumptions!E28</f>
         <v/>
       </c>
       <c r="H7" s="29">
-        <f>Assumptions!F26</f>
+        <f>Assumptions!F28</f>
         <v/>
       </c>
       <c r="I7" s="29">
-        <f>Assumptions!G26</f>
+        <f>Assumptions!G28</f>
         <v/>
       </c>
     </row>
@@ -3941,14 +3933,14 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>37.3</v>
+        <v>35.3</v>
       </c>
       <c r="C6" s="29">
         <f>'SOTP Bridge'!C14</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -3963,14 +3955,14 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>29.2</v>
+        <v>28.2</v>
       </c>
       <c r="C7" s="29">
         <f>'SOTP Bridge'!C23</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>49.6</v>
+        <v>47.3</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
@@ -4055,7 +4047,7 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>37.3</v>
+        <v>35.29</v>
       </c>
       <c r="D13" s="23" t="n">
         <v>48.08</v>
@@ -4405,7 +4397,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.7078292485042049</v>
+        <v>0.7092581337669651</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -4431,480 +4423,466 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity Ke = rf* + beta x ERP</t>
-        </is>
-      </c>
-      <c r="B13" s="13">
-        <f>B10+B11*B12</f>
-        <v/>
+          <t xml:space="preserve">   of which the MATURE premium — beta applies to this leg only</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>0.042304</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>reproduces the schedule's own 8.589% from the three cells above it</t>
+          <t>Damodaran's identity: the total premium less the country leg below</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt — the company's own latest issue</t>
+          <t>Country premium — charged FLAT, once, never multiplied by beta</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>0.048602896</v>
+        <v>0.014896</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>the January 2026 sukuk in two tranches, weighted. Held against an effective rate computed independently over two periods from the finance cost on the borrowings that actually bear it.</t>
+          <t>the sovereign default spread scaled to equity volatility. Country risk is a charge on being here, not a charge that scales with a stock's covariance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>After-tax Kd</t>
+          <t>Cost of equity Ke = rf* + beta x MATURE premium + country premium, flat</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <f>B14*(1-0.200000)</f>
-        <v/>
+        <f>B10+B11*B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>reproduces the schedule's own 9.030% from the three cells above it</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Debt weight D/(D+E) — MARKET-VALUE equity, never book</t>
-        </is>
-      </c>
-      <c r="B16" s="13">
-        <f>23536.554/(B5*B6+23536.554)</f>
-        <v/>
+          <t>Pre-tax cost of debt — the company's own latest issue</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.048602896</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>gross borrowings from the LATEST DISCLOSED balance sheet</t>
+          <t>the January 2026 sukuk in two tranches, weighted. Held against an effective rate computed independently over two periods from the finance cost on the borrowings that actually bear it.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>WACC — FLAT, because the riyal is pegged and today is already the terminal</t>
+          <t>After-tax Kd</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <f>(1-B16)*B13+B16*B15</f>
-        <v/>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>the module returns a flat ladder here rather than manufacturing a glide the peg forbids; explicit 8.133% and terminal 8.133%</t>
-        </is>
+        <f>B16*(1-0.200000)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth — DERIVED, terminal inflation + stated real growth</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>0.02000000000000002</v>
+          <t>Debt weight D/(D+E) — MARKET-VALUE equity, never book</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>23536.554/(B5*B6+23536.554)</f>
+        <v/>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>real growth of 0.0% on the house terminal inflation. A typed nominal rate is unfalsifiable: nobody can tell whether 2.5% meant inflation plus half a point or something else.</t>
+          <t>gross borrowings from the LATEST DISCLOSED balance sheet</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>EV -&gt; EQUITY BRIDGE — every line from the committed bridge record</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>WACC — FLAT, because the riyal is pegged and today is already the terminal</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>(1-B18)*B15+B18*B17</f>
+        <v/>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>the module returns a flat ladder here rather than manufacturing a glide the peg forbids; explicit 8.531% and terminal 8.531%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Investments in associates and joint ventures</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>12909.648</v>
+          <t>Terminal growth — DERIVED, terminal inflation + stated real growth</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>0.02000000000000002</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>the FILED carrying value. The delivered study carried 4,641 — a figure from before the towers business was contributed to DIIC in February 2025 — and correcting it raised the answer by 3.55%.</t>
+          <t>real growth of 0.0% on the house terminal inflation. A typed nominal rate is unfalsifiable: nobody can tell whether 2.5% meant inflation plus half a point or something else.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Listed equity investment at its disclosed fair value</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>8513.43</v>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>marked at the disclosed fair value, not at cost</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>EV -&gt; EQUITY BRIDGE — every line from the committed bridge record</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Investment funds and unlisted equity investments, at fair value</t>
+          <t>Investments in associates and joint ventures</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>5163.516</v>
+        <v>12909.648</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>note 9.1, outside the operating cash flows this model discounts</t>
+          <t>the FILED carrying value. The delivered study carried 4,641 — a figure from before the towers business was contributed to DIIC in February 2025 — and correcting it raised the answer by 3.55%.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Net debt</t>
+          <t>Listed equity investment at its disclosed fair value</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>8375.406999999999</v>
+        <v>8513.43</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>borrowings 23537 + leases 2259 + spectrum licences 3443 less cash 12940, murabahas 1062, sukuk 6368 and treasury bills 492. THE SPECTRUM LICENCE LIABILITY is consideration owed for licences already capitalised and it is disclosed OUTSIDE borrowings, so a bridge reading the borrowings lines does not see it.</t>
+          <t>marked at the disclosed fair value, not at cost</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests, at their share of equity value</t>
+          <t>Investment funds and unlisted equity investments, at fair value</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>3921.206149602089</v>
+        <v>5163.516</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>the model capitalises 100% of subsidiary cash flow, so the minority's claim is worth its SHARE OF THAT VALUE and not its historical cost. Book is 2726 and is published beside it so a reader sees the choice.</t>
+          <t>note 9.1, outside the operating cash flows this model discounts</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>DDM (the locked SAR 0.55/quarter policy)</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>8375.406999999999</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>borrowings 23537 + leases 2259 + spectrum licences 3443 less cash 12940, murabahas 1062, sukuk 6368 and treasury bills 492. THE SPECTRUM LICENCE LIABILITY is consideration owed for licences already capitalised and it is disclosed OUTSIDE borrowings, so a bridge reading the borrowings lines does not see it.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>DPS path FY26E–FY30E (SAR)</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>2.55</v>
+          <t>Non-controlling interests, at their share of equity value</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>3713.096100738611</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>the model capitalises 100% of subsidiary cash flow, so the minority's claim is worth its SHARE OF THAT VALUE and not its historical cost. Book is 2726 and is published beside it so a reader sees the choice.</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>DDM terminal dividend growth</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>post-policy (2027+) payout growth ≈ EPS growth at ~75% payout</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>DDM (the locked SAR 0.55/quarter policy)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Minority share of equity value (proportional)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0.02020629560266924</v>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>the minority's own share of profit, which is how the cross-check lenses apply it: proportionally to the whole equity value including the stakes, rather than as a fixed deduction</t>
-        </is>
+          <t>DPS path FY26E–FY30E (SAR)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>CROSS-CHECKS — published beside the central, never averaged into it</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>DDM terminal dividend growth</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>post-policy (2027+) payout growth ≈ EPS growth at ~75% payout</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>EV/EBITDA — the company's own trailing multiple, three year ends</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>8.762062030257292</v>
+          <t>Minority share of equity value (proportional)</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>0.02020629560266924</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>bear 8.316x to bull 9.131x, the range its own three year ends span. NOT a peer band and NOT the current multiple.</t>
+          <t>the minority's own share of profit, which is how the cross-check lenses apply it: proportionally to the whole equity value including the stakes, rather than as a fixed deduction</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>FY26E net profit for the relative cross-check</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n">
-        <v>14503.30474307932</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>from the projected income statement, not aligned by hand</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>CROSS-CHECKS — published beside the central, never averaged into it</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Normalized PAT (ex one-offs)</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n">
-        <v>13232.64560847266</v>
+          <t>EV/EBITDA — the company's own trailing multiple, three year ends</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>8.762062030257292</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>bear 8.316x to bull 9.131x, the range its own three year ends span. NOT a peer band and NOT the current multiple.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Justified through-cycle P/E</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>15</v>
+          <t>FY26E net profit for the relative cross-check</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>14503.30474307932</v>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>a stated judgement rather than a measurement, and it is a CROSS-CHECK: it carries no weight in the central</t>
+          <t>from the projected income statement, not aligned by hand</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>THE RETIRED BLEND — recorded so nothing here can quietly rebuild it</t>
-        </is>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Normalized PAT (ex one-offs)</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>13232.64560847266</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Former weights: cash flow 35%, dividend discount 25%, relative 20%, normalised earnings 20%</t>
-        </is>
+          <t>Justified through-cycle P/E</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>RETIRED. Two of those four lenses are not permitted cross-checks for this class at all and between them carried 45% of a central.</t>
+          <t>a stated judgement rather than a measurement, and it is a CROSS-CHECK: it carries no weight in the central</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>THE PRICE MAP — the production engine, reproduced (outputs on the Monte Carlo sheet)</t>
+          <t>THE RETIRED BLEND — recorded so nothing here can quietly rebuild it</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Forward volatility over three months (annualised)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.1653</v>
+          <t>Former weights: cash flow 35%, dividend discount 25%, relative 20%, normalised earnings 20%</t>
+        </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Projected from this stock’s own recent, medium and longer-run variation</t>
+          <t>RETIRED. Two of those four lenses are not permitted cross-checks for this class at all and between them carried 45% of a central.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Tail parameter and width calibration</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>15.0 / 1.056</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>The market panel’s fitted pair. Neither is quoted alone: they trade off, and the honest object is the cone they jointly produce</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>THE PRICE MAP — the production engine, reproduced (outputs on the Monte Carlo sheet)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Momentum lean applied over three months</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>0.002404</v>
+          <t>Forward volatility over three months (annualised)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>0.1653</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Direction call UP (reading +0.30 against a 0.25 threshold); capped at the strength measured</t>
+          <t>Projected from this stock’s own recent, medium and longer-run variation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Tail parameter and width calibration</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>15.0 / 1.056</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>The market panel’s fitted pair. Neither is quoted alone: they trade off, and the honest object is the cone they jointly produce</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Momentum lean applied over three months</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>0.002404</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Direction call UP (reading +0.30 against a 0.25 threshold); capped at the strength measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
           <t>Paths / seed</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>50,000 / 42</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>FORECAST DRIVERS (FY26E–FY30E) — top-down (§3.5-C gate: subs × ARPU not disclosed)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Driver \ year</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Sirar — real revenue growth</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>0.13170363</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>0.09877772999999999</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.06585182000000001</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>0.03292591</v>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>stc Bank — real revenue growth</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>0.10263522</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0.07697641</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.05131761</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>0.0256588</v>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Specialized — real revenue growth</t>
+          <t>Sirar — real revenue growth</t>
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>-0.05664896</v>
+        <v>0.13170363</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>-0.04248672</v>
+        <v>0.09877772999999999</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>-0.02832448</v>
+        <v>0.06585182000000001</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>-0.01416224</v>
+        <v>0.03292591</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>0</v>
@@ -4913,20 +4891,20 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Solutions — real revenue growth</t>
+          <t>stc Bank — real revenue growth</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>0.0442675</v>
+        <v>0.10263522</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.03320063</v>
+        <v>0.07697641</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.02213375</v>
+        <v>0.05131761</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>0.01106688</v>
+        <v>0.0256588</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>0</v>
@@ -4935,20 +4913,20 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Center 3 — real revenue growth</t>
+          <t>Specialized — real revenue growth</t>
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>0.01866393</v>
+        <v>-0.05664896</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.01399795</v>
+        <v>-0.04248672</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.00933197</v>
+        <v>-0.02832448</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>0.00466598</v>
+        <v>-0.01416224</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>0</v>
@@ -4957,20 +4935,20 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>iot2 — real revenue growth</t>
+          <t>Solutions — real revenue growth</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>0.01866393</v>
+        <v>0.0442675</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.01399795</v>
+        <v>0.03320063</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>0.00933197</v>
+        <v>0.02213375</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>0.00466598</v>
+        <v>0.01106688</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>0</v>
@@ -4979,7 +4957,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>SCCC — real revenue growth</t>
+          <t>Center 3 — real revenue growth</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
@@ -5001,7 +4979,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Other operating segments — real revenue growth</t>
+          <t>iot2 — real revenue growth</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
@@ -5023,20 +5001,20 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Channels — real revenue growth</t>
+          <t>SCCC — real revenue growth</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>-0.01678193</v>
+        <v>0.01866393</v>
       </c>
       <c r="D51" s="10" t="n">
-        <v>-0.01258645</v>
+        <v>0.01399795</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>-0.008390959999999999</v>
+        <v>0.00933197</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>-0.00419548</v>
+        <v>0.00466598</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>0</v>
@@ -5045,20 +5023,20 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>stc Kuwait — real revenue growth</t>
+          <t>Other operating segments — real revenue growth</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>0.00513056</v>
+        <v>0.01866393</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.00384792</v>
+        <v>0.01399795</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.00256528</v>
+        <v>0.00933197</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>0.00128264</v>
+        <v>0.00466598</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
@@ -5067,20 +5045,20 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>stc Bahrain — real revenue growth</t>
+          <t>Channels — real revenue growth</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>-0.00262868</v>
+        <v>-0.01678193</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>-0.00197151</v>
+        <v>-0.01258645</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.00131434</v>
+        <v>-0.008390959999999999</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>-0.00065717</v>
+        <v>-0.00419548</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>0</v>
@@ -5089,20 +5067,20 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>stc — real revenue growth</t>
+          <t>stc Kuwait — real revenue growth</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>0.00181084</v>
+        <v>0.00513056</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.00175477</v>
+        <v>0.00384792</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.00143427</v>
+        <v>0.00256528</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>0.00084935</v>
+        <v>0.00128264</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>0</v>
@@ -5111,287 +5089,309 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>First-year scale onto the reviewed half (annualised)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>1.006082103803541</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>1</v>
+          <t>stc Bahrain — real revenue growth</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>-0.00262868</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>-0.00197151</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.00131434</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>-0.00065717</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>House Saudi inflation ladder (nominal = real x this)</t>
+          <t>stc — real revenue growth</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>0.023</v>
+        <v>0.00181084</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.021</v>
+        <v>0.00175477</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.02</v>
+        <v>0.00143427</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>0.02</v>
+        <v>0.00084935</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Inter-segment eliminations (% of gross segment revenue)</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>-0.128739252364491</v>
-      </c>
-      <c r="D57" s="10" t="n">
-        <v>-0.128739252364491</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.128739252364491</v>
-      </c>
-      <c r="F57" s="10" t="n">
-        <v>-0.128739252364491</v>
-      </c>
-      <c r="G57" s="10" t="n">
-        <v>-0.128739252364491</v>
+          <t>First-year scale onto the reviewed half (annualised)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>1.006082103803541</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Group EBITDA margin</t>
+          <t>House Saudi inflation ladder (nominal = real x this)</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>0.3205740707168828</v>
+        <v>0.023</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.3197807704348273</v>
+        <v>0.021</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.319055773120738</v>
+        <v>0.02</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>0.318382960635945</v>
+        <v>0.02</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>0.3177323370749691</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>D&amp;A (% of revenue)</t>
+          <t>Inter-segment eliminations (% of gross segment revenue)</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>0.128904417866277</v>
+        <v>-0.128739252364491</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.128904417866277</v>
+        <v>-0.128739252364491</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.128904417866277</v>
+        <v>-0.128739252364491</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>0.128904417866277</v>
+        <v>-0.128739252364491</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0.128904417866277</v>
+        <v>-0.128739252364491</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Capex intensity (% of revenue)</t>
+          <t>Group EBITDA margin</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>0.1496340450713096</v>
+        <v>0.3205740707168828</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.1496340450713096</v>
+        <v>0.3197807704348273</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.1496340450713096</v>
+        <v>0.319055773120738</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>0.1496340450713096</v>
+        <v>0.318382960635945</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>0.1496340450713096</v>
+        <v>0.3177323370749691</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Working-capital movement (% of revenue, an OUTPUT of the cycle)</t>
+          <t>D&amp;A (% of revenue)</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>-9.011973604334838e-17</v>
+        <v>0.128904417866277</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.004752892568147541</v>
+        <v>0.128904417866277</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>0.004271372312109522</v>
+        <v>0.128904417866277</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>0.003883270351596636</v>
+        <v>0.128904417866277</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>0.003439410244856249</v>
+        <v>0.128904417866277</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Finance income (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="n">
-        <v>951.7174030437861</v>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>971.7034685077056</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>991.1375378778597</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>1010.960288635417</v>
-      </c>
-      <c r="G62" s="9" t="n">
-        <v>1031.179494408125</v>
+          <t>Capex intensity (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>0.1496340450713096</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>0.1496340450713096</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.1496340450713096</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>0.1496340450713096</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>0.1496340450713096</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Finance cost (SAR mn)</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="n">
-        <v>-1443.591305740267</v>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>-1473.906723160813</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>-1503.384857624029</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>-1533.45255477651</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>-1564.12160587204</v>
+          <t>Working-capital movement (% of revenue, an OUTPUT of the cycle)</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>-9.011973604334838e-17</v>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>0.004752892568147541</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.004271372312109522</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>0.003883270351596636</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>0.003439410244856249</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Early retirement programme (SAR mn, three-year mean escalated)</t>
+          <t>Finance income (SAR mn)</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>-1421.299666666667</v>
+        <v>951.7174030437861</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>-1451.146959666667</v>
+        <v>971.7034685077056</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>-1480.16989886</v>
+        <v>991.1375378778597</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>-1509.7732968372</v>
+        <v>1010.960288635417</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>-1539.968762773944</v>
+        <v>1031.179494408125</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Effective zakat rate (three filed years together)</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>0.08266854587581883</v>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>0.08266854587581883</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.08266854587581883</v>
-      </c>
-      <c r="F65" s="10" t="n">
-        <v>0.08266854587581883</v>
-      </c>
-      <c r="G65" s="10" t="n">
-        <v>0.08266854587581883</v>
+          <t>Finance cost (SAR mn)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>-1443.591305740267</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>-1473.906723160813</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>-1503.384857624029</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>-1533.45255477651</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>-1564.12160587204</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
+          <t>Early retirement programme (SAR mn, three-year mean escalated)</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>-1421.299666666667</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>-1451.146959666667</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>-1480.16989886</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>-1509.7732968372</v>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>-1539.968762773944</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Effective zakat rate (three filed years together)</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>0.08266854587581883</v>
+      </c>
+      <c r="D67" s="10" t="n">
+        <v>0.08266854587581883</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.08266854587581883</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>0.08266854587581883</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>0.08266854587581883</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>DPS declared (SAR/share)</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C68" s="7" t="n">
         <v>2.2</v>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="D68" s="7" t="n">
         <v>2.2</v>
       </c>
-      <c r="E66" s="7" t="n">
+      <c r="E68" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F68" s="7" t="n">
         <v>2.4</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G68" s="7" t="n">
         <v>2.55</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Gross margin (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="G68" s="10" t="n">
-        <v>0.485</v>
       </c>
     </row>
     <row r="84">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>A 4.91-year weekly regression of stc against the published index of the exchange it is listed on, the Tadawul All Share Index, read as of 2026-08-18: 252 paired weeks on that exchange’s own trading week, beta 0.7078, standard error 0.1029, R² 30.2%, and a confidence interval running 0.5386 to 0.8771. It is the first tier of the house preference order rather than a stopgap. A superseded reading of 0.4800, taken from a nine-week daily window on a commercial vendor’s index quotes, is recorded in the bibliography and is not used. Sensitivity: at a beta of 1.00 the cost of equity is 10.26% and the cost of capital 9.64%, which the beta grid on the Sensitivity sheet prices in full.</t>
+          <t>A 4.94-year weekly regression of stc against the published index of the exchange it is listed on, the Tadawul All Share Index, read as of 2026-09-08: 254 paired weeks on that exchange’s own trading week, beta 0.7093, standard error 0.1022, R² 30.3%, and a confidence interval running 0.5412 to 0.8773. It is the first tier of the house preference order rather than a stopgap. A superseded reading of 0.4800, taken from a nine-week daily window on a commercial vendor’s index quotes, is recorded in the bibliography and is not used. Sensitivity: at a beta of 1.00 the cost of equity is 10.26% and the cost of capital 9.64%, which the beta grid on the Sensitivity sheet prices in full.</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>The cost of capital is built the same way for every market this desk covers: the sovereign yield for the country, less that same sovereign’s own default spread so country risk is charged once rather than twice, plus beta times an equity risk premium published for Saudi Arabia specifically. Both premium bases are published — 5.72% central and 5.01% on the alternative — giving costs of capital of 8.13% and 8.10%, so the choice is visible rather than made silently.</t>
+          <t>The cost of capital is built the same way for every market this desk covers: the sovereign yield for the country, less that same sovereign’s own default spread so country risk is charged once rather than twice, plus beta times an equity risk premium published for Saudi Arabia specifically. Both premium bases are published — 5.72% central and 5.01% on the alternative — giving costs of capital of 8.53% and 8.31%, so the choice is visible rather than made silently.</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="C8" s="19">
-        <f>Assumptions!$B$20</f>
+        <f>Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="C9" s="19">
-        <f>Assumptions!$B$21</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C10" s="19">
-        <f>Assumptions!$B$22</f>
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="C11" s="19">
-        <f>-Assumptions!$B$23</f>
+        <f>-Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="C12" s="19">
-        <f>-Assumptions!$B$24</f>
+        <f>-Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="25">
-        <f>C6+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23-Assumptions!$B$24</f>
+        <f>C6+Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24-Assumptions!$B$25-Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -5720,23 +5720,23 @@
         </is>
       </c>
       <c r="C18" s="29">
-        <f>Assumptions!C26</f>
+        <f>Assumptions!C28</f>
         <v/>
       </c>
       <c r="D18" s="29">
-        <f>Assumptions!D26</f>
+        <f>Assumptions!D28</f>
         <v/>
       </c>
       <c r="E18" s="29">
-        <f>Assumptions!E26</f>
+        <f>Assumptions!E28</f>
         <v/>
       </c>
       <c r="F18" s="29">
-        <f>Assumptions!F26</f>
+        <f>Assumptions!F28</f>
         <v/>
       </c>
       <c r="G18" s="29">
-        <f>Assumptions!G26</f>
+        <f>Assumptions!G28</f>
         <v/>
       </c>
     </row>
@@ -5747,23 +5747,23 @@
         </is>
       </c>
       <c r="C19" s="26">
-        <f>C18/(1+Assumptions!$B$13)^1</f>
+        <f>C18/(1+Assumptions!$B$15)^1</f>
         <v/>
       </c>
       <c r="D19" s="26">
-        <f>D18/(1+Assumptions!$B$13)^2</f>
+        <f>D18/(1+Assumptions!$B$15)^2</f>
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>E18/(1+Assumptions!$B$13)^3</f>
+        <f>E18/(1+Assumptions!$B$15)^3</f>
         <v/>
       </c>
       <c r="F19" s="26">
-        <f>F18/(1+Assumptions!$B$13)^4</f>
+        <f>F18/(1+Assumptions!$B$15)^4</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>G18/(1+Assumptions!$B$13)^5</f>
+        <f>G18/(1+Assumptions!$B$15)^5</f>
         <v/>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="C21" s="26">
-        <f>G18*(1+Assumptions!$B$27)/(Assumptions!$B$13-Assumptions!$B$27)</f>
+        <f>G18*(1+Assumptions!$B$29)/(Assumptions!$B$15-Assumptions!$B$29)</f>
         <v/>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="C22" s="26">
-        <f>C21/(1+Assumptions!$B$13)^5</f>
+        <f>C21/(1+Assumptions!$B$15)^5</f>
         <v/>
       </c>
     </row>
@@ -5937,23 +5937,23 @@
         <v>51119.024</v>
       </c>
       <c r="E6" s="17">
-        <f>D6*(1+Assumptions!$C$54)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D6*(1+Assumptions!$C$56)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>E6*(1+Assumptions!$D$54)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E6*(1+Assumptions!$D$56)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>F6*(1+Assumptions!$E$54)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F6*(1+Assumptions!$E$56)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>G6*(1+Assumptions!$F$54)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G6*(1+Assumptions!$F$56)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I6" s="17">
-        <f>H6*(1+Assumptions!$G$54)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H6*(1+Assumptions!$G$56)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -5973,23 +5973,23 @@
         <v>14085.195</v>
       </c>
       <c r="E7" s="17">
-        <f>D7*(1+Assumptions!$C$51)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D7*(1+Assumptions!$C$53)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>E7*(1+Assumptions!$D$51)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E7*(1+Assumptions!$D$53)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>F7*(1+Assumptions!$E$51)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F7*(1+Assumptions!$E$53)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>G7*(1+Assumptions!$F$51)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G7*(1+Assumptions!$F$53)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I7" s="17">
-        <f>H7*(1+Assumptions!$G$51)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H7*(1+Assumptions!$G$53)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6009,23 +6009,23 @@
         <v>12730.189</v>
       </c>
       <c r="E8" s="17">
-        <f>D8*(1+Assumptions!$C$46)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D8*(1+Assumptions!$C$48)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>E8*(1+Assumptions!$D$46)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E8*(1+Assumptions!$D$48)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>F8*(1+Assumptions!$E$46)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F8*(1+Assumptions!$E$48)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>G8*(1+Assumptions!$F$46)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G8*(1+Assumptions!$F$48)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>H8*(1+Assumptions!$G$46)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H8*(1+Assumptions!$G$48)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6045,23 +6045,23 @@
         <v>4179.842</v>
       </c>
       <c r="E9" s="17">
-        <f>D9*(1+Assumptions!$C$52)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D9*(1+Assumptions!$C$54)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>E9*(1+Assumptions!$D$52)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E9*(1+Assumptions!$D$54)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>F9*(1+Assumptions!$E$52)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F9*(1+Assumptions!$E$54)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>G9*(1+Assumptions!$F$52)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G9*(1+Assumptions!$F$54)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>H9*(1+Assumptions!$G$52)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H9*(1+Assumptions!$G$54)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6081,23 +6081,23 @@
         <v>1967.83</v>
       </c>
       <c r="E10" s="17">
-        <f>D10*(1+Assumptions!$C$53)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D10*(1+Assumptions!$C$55)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>E10*(1+Assumptions!$D$53)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E10*(1+Assumptions!$D$55)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>F10*(1+Assumptions!$E$53)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F10*(1+Assumptions!$E$55)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>G10*(1+Assumptions!$F$53)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G10*(1+Assumptions!$F$55)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>H10*(1+Assumptions!$G$53)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H10*(1+Assumptions!$G$55)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6117,23 +6117,23 @@
         <v>1961.666</v>
       </c>
       <c r="E11" s="17">
-        <f>D11*(1+Assumptions!$C$47)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D11*(1+Assumptions!$C$49)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>E11*(1+Assumptions!$D$47)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E11*(1+Assumptions!$D$49)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>F11*(1+Assumptions!$E$47)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F11*(1+Assumptions!$E$49)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>G11*(1+Assumptions!$F$47)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G11*(1+Assumptions!$F$49)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>H11*(1+Assumptions!$G$47)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H11*(1+Assumptions!$G$49)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6153,23 +6153,23 @@
         <v>1401.027</v>
       </c>
       <c r="E12" s="17">
-        <f>D12*(1+Assumptions!$C$44)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D12*(1+Assumptions!$C$46)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>E12*(1+Assumptions!$D$44)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E12*(1+Assumptions!$D$46)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G12" s="17">
-        <f>F12*(1+Assumptions!$E$44)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F12*(1+Assumptions!$E$46)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H12" s="17">
-        <f>G12*(1+Assumptions!$F$44)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G12*(1+Assumptions!$F$46)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I12" s="17">
-        <f>H12*(1+Assumptions!$G$44)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H12*(1+Assumptions!$G$46)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6189,23 +6189,23 @@
         <v>826.545</v>
       </c>
       <c r="E13" s="17">
-        <f>D13*(1+Assumptions!$C$43)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D13*(1+Assumptions!$C$45)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>E13*(1+Assumptions!$D$43)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E13*(1+Assumptions!$D$45)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>F13*(1+Assumptions!$E$43)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F13*(1+Assumptions!$E$45)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>G13*(1+Assumptions!$F$43)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G13*(1+Assumptions!$F$45)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>H13*(1+Assumptions!$G$43)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H13*(1+Assumptions!$G$45)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6225,23 +6225,23 @@
         <v>355.306</v>
       </c>
       <c r="E14" s="17">
-        <f>D14*(1+Assumptions!$C$45)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D14*(1+Assumptions!$C$47)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>E14*(1+Assumptions!$D$45)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E14*(1+Assumptions!$D$47)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>F14*(1+Assumptions!$E$45)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F14*(1+Assumptions!$E$47)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H14" s="17">
-        <f>G14*(1+Assumptions!$F$45)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G14*(1+Assumptions!$F$47)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>H14*(1+Assumptions!$G$45)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H14*(1+Assumptions!$G$47)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6261,23 +6261,23 @@
         <v>321.668</v>
       </c>
       <c r="E15" s="17">
-        <f>D15*(1+Assumptions!$C$48)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D15*(1+Assumptions!$C$50)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>E15*(1+Assumptions!$D$48)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E15*(1+Assumptions!$D$50)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>F15*(1+Assumptions!$E$48)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F15*(1+Assumptions!$E$50)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H15" s="17">
-        <f>G15*(1+Assumptions!$F$48)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G15*(1+Assumptions!$F$50)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>H15*(1+Assumptions!$G$48)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H15*(1+Assumptions!$G$50)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6297,23 +6297,23 @@
         <v>303.969</v>
       </c>
       <c r="E16" s="17">
-        <f>D16*(1+Assumptions!$C$49)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D16*(1+Assumptions!$C$51)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>E16*(1+Assumptions!$D$49)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E16*(1+Assumptions!$D$51)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>F16*(1+Assumptions!$E$49)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F16*(1+Assumptions!$E$51)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>G16*(1+Assumptions!$F$49)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G16*(1+Assumptions!$F$51)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>H16*(1+Assumptions!$G$49)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H16*(1+Assumptions!$G$51)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6333,23 +6333,23 @@
         <v>65.059</v>
       </c>
       <c r="E17" s="17">
-        <f>D17*(1+Assumptions!$C$50)*(1+Assumptions!$C$56)*Assumptions!$C$55</f>
+        <f>D17*(1+Assumptions!$C$52)*(1+Assumptions!$C$58)*Assumptions!$C$57</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>E17*(1+Assumptions!$D$50)*(1+Assumptions!$D$56)*Assumptions!$D$55</f>
+        <f>E17*(1+Assumptions!$D$52)*(1+Assumptions!$D$58)*Assumptions!$D$57</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>F17*(1+Assumptions!$E$50)*(1+Assumptions!$E$56)*Assumptions!$E$55</f>
+        <f>F17*(1+Assumptions!$E$52)*(1+Assumptions!$E$58)*Assumptions!$E$57</f>
         <v/>
       </c>
       <c r="H17" s="17">
-        <f>G17*(1+Assumptions!$F$50)*(1+Assumptions!$F$56)*Assumptions!$F$55</f>
+        <f>G17*(1+Assumptions!$F$52)*(1+Assumptions!$F$58)*Assumptions!$F$57</f>
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>H17*(1+Assumptions!$G$50)*(1+Assumptions!$G$56)*Assumptions!$G$55</f>
+        <f>H17*(1+Assumptions!$G$52)*(1+Assumptions!$G$58)*Assumptions!$G$57</f>
         <v/>
       </c>
     </row>
@@ -6408,23 +6408,23 @@
         <v>-11498.645</v>
       </c>
       <c r="E19" s="17">
-        <f>E18*Assumptions!$C$57</f>
+        <f>E18*Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>F18*Assumptions!$D$57</f>
+        <f>F18*Assumptions!$D$59</f>
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>G18*Assumptions!$E$57</f>
+        <f>G18*Assumptions!$E$59</f>
         <v/>
       </c>
       <c r="H19" s="17">
-        <f>H18*Assumptions!$F$57</f>
+        <f>H18*Assumptions!$F$59</f>
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>I18*Assumptions!$G$57</f>
+        <f>I18*Assumptions!$G$59</f>
         <v/>
       </c>
     </row>
@@ -6483,23 +6483,23 @@
         <v>24469</v>
       </c>
       <c r="E22" s="17">
-        <f>E20*Assumptions!$C$58</f>
+        <f>E20*Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>F20*Assumptions!$D$58</f>
+        <f>F20*Assumptions!$D$60</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>G20*Assumptions!$E$58</f>
+        <f>G20*Assumptions!$E$60</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>H20*Assumptions!$F$58</f>
+        <f>H20*Assumptions!$F$60</f>
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>I20*Assumptions!$G$58</f>
+        <f>I20*Assumptions!$G$60</f>
         <v/>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="C6" s="29">
-        <f>(DCF!B7*Assumptions!$B$30+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23)*(1-Assumptions!$B$28)/Assumptions!$B$6</f>
+        <f>(DCF!B7*Assumptions!$B$32+Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24-Assumptions!$B$25)*(1-Assumptions!$B$30)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="C7" s="33">
-        <f>C6*Assumptions!$B$6/Assumptions!$B$31</f>
+        <f>C6*Assumptions!$B$6/Assumptions!$B$33</f>
         <v/>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="C9" s="29">
-        <f>Assumptions!$B$32*Assumptions!$B$33/Assumptions!$B$6</f>
+        <f>Assumptions!$B$34*Assumptions!$B$35/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="C10" s="29">
-        <f>Assumptions!$B$32/Assumptions!$B$6</f>
+        <f>Assumptions!$B$34/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -6825,23 +6825,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>-B6*Assumptions!$C$59</f>
+        <f>-B6*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>-C6*Assumptions!$D$59</f>
+        <f>-C6*Assumptions!$D$61</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>-D6*Assumptions!$E$59</f>
+        <f>-D6*Assumptions!$E$61</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>-E6*Assumptions!$F$59</f>
+        <f>-E6*Assumptions!$F$61</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>-F6*Assumptions!$G$59</f>
+        <f>-F6*Assumptions!$G$61</f>
         <v/>
       </c>
     </row>
@@ -6933,23 +6933,23 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>-B6*Assumptions!$C$60</f>
+        <f>-B6*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="C12" s="17">
-        <f>-C6*Assumptions!$D$60</f>
+        <f>-C6*Assumptions!$D$62</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>-D6*Assumptions!$E$60</f>
+        <f>-D6*Assumptions!$E$62</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>-E6*Assumptions!$F$60</f>
+        <f>-E6*Assumptions!$F$62</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>-F6*Assumptions!$G$60</f>
+        <f>-F6*Assumptions!$G$62</f>
         <v/>
       </c>
     </row>
@@ -6960,23 +6960,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>-B6*Assumptions!$C$61</f>
+        <f>-B6*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>-C6*Assumptions!$D$61</f>
+        <f>-C6*Assumptions!$D$63</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>-D6*Assumptions!$E$61</f>
+        <f>-D6*Assumptions!$E$63</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>-E6*Assumptions!$F$61</f>
+        <f>-E6*Assumptions!$F$63</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>-F6*Assumptions!$G$61</f>
+        <f>-F6*Assumptions!$G$63</f>
         <v/>
       </c>
     </row>
@@ -7014,23 +7014,23 @@
         </is>
       </c>
       <c r="B15" s="21">
-        <f>1/(1+Assumptions!$B$17)^1</f>
+        <f>1/(1+Assumptions!$B$19)^1</f>
         <v/>
       </c>
       <c r="C15" s="21">
-        <f>1/(1+Assumptions!$B$17)^2</f>
+        <f>1/(1+Assumptions!$B$19)^2</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>1/(1+Assumptions!$B$17)^3</f>
+        <f>1/(1+Assumptions!$B$19)^3</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>1/(1+Assumptions!$B$17)^4</f>
+        <f>1/(1+Assumptions!$B$19)^4</f>
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>1/(1+Assumptions!$B$17)^5</f>
+        <f>1/(1+Assumptions!$B$19)^5</f>
         <v/>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="B25" s="17">
-        <f>B24*(1+Assumptions!$B$18)/(Assumptions!$B$17-Assumptions!$B$18)</f>
+        <f>B24*(1+Assumptions!$B$20)/(Assumptions!$B$19-Assumptions!$B$20)</f>
         <v/>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>Assumptions!$B$20</f>
+        <f>Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B30" s="17">
-        <f>Assumptions!$B$21</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>-Assumptions!$B$23</f>
+        <f>-Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B32" s="17">
-        <f>-Assumptions!$B$24</f>
+        <f>-Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="B33" s="17">
-        <f>Assumptions!$B$22</f>
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B34" s="20">
-        <f>B27+Assumptions!$B$20+Assumptions!$B$21+Assumptions!$B$22-Assumptions!$B$23-Assumptions!$B$24</f>
+        <f>B27+Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24-Assumptions!$B$25-Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -7416,23 +7416,23 @@
         <v>37700</v>
       </c>
       <c r="E7" s="17">
-        <f>E6*Assumptions!$C$68</f>
+        <f>E6*0.485</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>F6*Assumptions!$D$68</f>
+        <f>F6*0.485</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>G6*Assumptions!$E$68</f>
+        <f>G6*0.485</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>H6*Assumptions!$F$68</f>
+        <f>H6*0.485</f>
         <v/>
       </c>
       <c r="I7" s="17">
-        <f>I6*Assumptions!$G$68</f>
+        <f>I6*0.485</f>
         <v/>
       </c>
     </row>
@@ -7566,23 +7566,23 @@
         <v>-10031</v>
       </c>
       <c r="E11" s="17">
-        <f>-E6*Assumptions!$C$59</f>
+        <f>-E6*Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>-F6*Assumptions!$D$59</f>
+        <f>-F6*Assumptions!$D$61</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>-G6*Assumptions!$E$59</f>
+        <f>-G6*Assumptions!$E$61</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>-H6*Assumptions!$F$59</f>
+        <f>-H6*Assumptions!$F$61</f>
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>-I6*Assumptions!$G$59</f>
+        <f>-I6*Assumptions!$G$61</f>
         <v/>
       </c>
     </row>
@@ -7625,36 +7625,36 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Associates, net finance, impairments &amp; other</t>
+          <t>Share of associates &amp; JVs + net finance &amp; other</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>826</v>
+        <v>1461</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>-2292</v>
+        <v>899</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>285</v>
       </c>
       <c r="E13" s="17">
-        <f>Assumptions!$C$62+Assumptions!$C$63+Assumptions!$C$64</f>
+        <f>Assumptions!$C$64+Assumptions!$C$65+Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>Assumptions!$D$62+Assumptions!$D$63+Assumptions!$D$64</f>
+        <f>Assumptions!$D$64+Assumptions!$D$65+Assumptions!$D$66</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>Assumptions!$E$62+Assumptions!$E$63+Assumptions!$E$64</f>
+        <f>Assumptions!$E$64+Assumptions!$E$65+Assumptions!$E$66</f>
         <v/>
       </c>
       <c r="H13" s="17">
-        <f>Assumptions!$F$62+Assumptions!$F$63+Assumptions!$F$64</f>
+        <f>Assumptions!$F$64+Assumptions!$F$65+Assumptions!$F$66</f>
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>Assumptions!$G$62+Assumptions!$G$63+Assumptions!$G$64</f>
+        <f>Assumptions!$G$64+Assumptions!$G$65+Assumptions!$G$66</f>
         <v/>
       </c>
     </row>
@@ -7664,13 +7664,13 @@
           <t>Profit before zakat &amp; income tax</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>13987</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>12134</v>
-      </c>
-      <c r="D14" s="9" t="n">
+      <c r="B14" s="20" t="n">
+        <v>14622</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>15325</v>
+      </c>
+      <c r="D14" s="20" t="n">
         <v>14723</v>
       </c>
       <c r="E14" s="20">
